--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126964</v>
+        <v>122126959</v>
       </c>
       <c r="B2" t="n">
         <v>56273</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491408</v>
+        <v>491397</v>
       </c>
       <c r="R2" t="n">
-        <v>6278312</v>
+        <v>6278316</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126295</v>
+        <v>122126066</v>
       </c>
       <c r="B3" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,25 +831,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491408</v>
+        <v>491433</v>
       </c>
       <c r="R3" t="n">
-        <v>6278313</v>
+        <v>6278305</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,10 +963,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126297</v>
+        <v>122126050</v>
       </c>
       <c r="B4" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,25 +975,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491410</v>
+        <v>491450</v>
       </c>
       <c r="R4" t="n">
-        <v>6278308</v>
+        <v>6278297</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,22 +1047,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1107,7 +1107,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126082</v>
+        <v>122126064</v>
       </c>
       <c r="B5" t="n">
         <v>56266</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491466</v>
+        <v>491433</v>
       </c>
       <c r="R5" t="n">
-        <v>6278292</v>
+        <v>6278303</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126974</v>
+        <v>122126144</v>
       </c>
       <c r="B7" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1407,25 +1407,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491407</v>
+        <v>491449</v>
       </c>
       <c r="R7" t="n">
-        <v>6278314</v>
+        <v>6278298</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1479,22 +1479,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126063</v>
+        <v>122126306</v>
       </c>
       <c r="B8" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1551,25 +1551,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491433</v>
+        <v>491432</v>
       </c>
       <c r="R8" t="n">
-        <v>6278302</v>
+        <v>6278301</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126971</v>
+        <v>122126963</v>
       </c>
       <c r="B9" t="n">
         <v>56273</v>
@@ -1740,7 +1740,7 @@
         <v>491408</v>
       </c>
       <c r="R9" t="n">
-        <v>6278315</v>
+        <v>6278312</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122126961</v>
+        <v>122126974</v>
       </c>
       <c r="B10" t="n">
         <v>56273</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491402</v>
+        <v>491407</v>
       </c>
       <c r="R10" t="n">
         <v>6278314</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1971,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126968</v>
+        <v>122126082</v>
       </c>
       <c r="B11" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491408</v>
+        <v>491466</v>
       </c>
       <c r="R11" t="n">
-        <v>6278314</v>
+        <v>6278292</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2115,7 +2115,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122126970</v>
+        <v>122126983</v>
       </c>
       <c r="B12" t="n">
         <v>56273</v>
@@ -2172,7 +2172,7 @@
         <v>491409</v>
       </c>
       <c r="R12" t="n">
-        <v>6278314</v>
+        <v>6278308</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2403,7 +2403,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122126298</v>
+        <v>122126299</v>
       </c>
       <c r="B14" t="n">
         <v>56285</v>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491410</v>
+        <v>491409</v>
       </c>
       <c r="R14" t="n">
         <v>6278309</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122126079</v>
+        <v>122126298</v>
       </c>
       <c r="B15" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2559,25 +2559,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491470</v>
+        <v>491410</v>
       </c>
       <c r="R15" t="n">
-        <v>6278289</v>
+        <v>6278309</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122126306</v>
+        <v>122126081</v>
       </c>
       <c r="B16" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491432</v>
+        <v>491467</v>
       </c>
       <c r="R16" t="n">
-        <v>6278301</v>
+        <v>6278291</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122126144</v>
+        <v>122126973</v>
       </c>
       <c r="B17" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2847,25 +2847,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491449</v>
+        <v>491408</v>
       </c>
       <c r="R17" t="n">
-        <v>6278298</v>
+        <v>6278314</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2919,22 +2919,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2979,10 +2979,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122126070</v>
+        <v>122126296</v>
       </c>
       <c r="B18" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2991,25 +2991,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491431</v>
+        <v>491410</v>
       </c>
       <c r="R18" t="n">
-        <v>6278302</v>
+        <v>6278308</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3267,7 +3267,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122126977</v>
+        <v>122126969</v>
       </c>
       <c r="B20" t="n">
         <v>56273</v>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R20" t="n">
-        <v>6278313</v>
+        <v>6278314</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3411,7 +3411,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122126982</v>
+        <v>122126975</v>
       </c>
       <c r="B21" t="n">
         <v>56273</v>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491409</v>
+        <v>491407</v>
       </c>
       <c r="R21" t="n">
-        <v>6278309</v>
+        <v>6278313</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122126060</v>
+        <v>122126272</v>
       </c>
       <c r="B22" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3567,25 +3567,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491410</v>
+        <v>491444</v>
       </c>
       <c r="R22" t="n">
-        <v>6278308</v>
+        <v>6278302</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3639,22 +3639,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122125947</v>
+        <v>122126063</v>
       </c>
       <c r="B23" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3711,25 +3711,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491408</v>
+        <v>491433</v>
       </c>
       <c r="R23" t="n">
-        <v>6278313</v>
+        <v>6278302</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122125950</v>
+        <v>122126146</v>
       </c>
       <c r="B24" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3855,25 +3855,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491430</v>
+        <v>491408</v>
       </c>
       <c r="R24" t="n">
-        <v>6278303</v>
+        <v>6278310</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3927,22 +3927,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3987,7 +3987,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122126076</v>
+        <v>122126079</v>
       </c>
       <c r="B25" t="n">
         <v>56266</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491469</v>
+        <v>491470</v>
       </c>
       <c r="R25" t="n">
         <v>6278289</v>
@@ -4076,17 +4076,17 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
+          <t>23:21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
           <t>23:22</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>23:23</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4131,7 +4131,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122126050</v>
+        <v>122126073</v>
       </c>
       <c r="B26" t="n">
         <v>56266</v>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491450</v>
+        <v>491432</v>
       </c>
       <c r="R26" t="n">
-        <v>6278297</v>
+        <v>6278302</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4215,22 +4215,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4275,10 +4275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122126273</v>
+        <v>122125948</v>
       </c>
       <c r="B27" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491430</v>
+        <v>491408</v>
       </c>
       <c r="R27" t="n">
-        <v>6278304</v>
+        <v>6278313</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4359,22 +4359,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122126975</v>
+        <v>122126062</v>
       </c>
       <c r="B28" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491407</v>
+        <v>491432</v>
       </c>
       <c r="R28" t="n">
-        <v>6278313</v>
+        <v>6278301</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4563,7 +4563,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126073</v>
+        <v>122126060</v>
       </c>
       <c r="B29" t="n">
         <v>56266</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491432</v>
+        <v>491410</v>
       </c>
       <c r="R29" t="n">
-        <v>6278302</v>
+        <v>6278308</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4707,10 +4707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122125949</v>
+        <v>122126978</v>
       </c>
       <c r="B30" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R30" t="n">
-        <v>6278312</v>
+        <v>6278313</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4851,10 +4851,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126301</v>
+        <v>122126069</v>
       </c>
       <c r="B31" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4863,25 +4863,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491409</v>
+        <v>491431</v>
       </c>
       <c r="R31" t="n">
-        <v>6278308</v>
+        <v>6278302</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4995,10 +4995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122126300</v>
+        <v>122125950</v>
       </c>
       <c r="B32" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491409</v>
+        <v>491430</v>
       </c>
       <c r="R32" t="n">
-        <v>6278309</v>
+        <v>6278303</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5139,7 +5139,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122126294</v>
+        <v>122126305</v>
       </c>
       <c r="B33" t="n">
         <v>56285</v>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491408</v>
+        <v>491431</v>
       </c>
       <c r="R33" t="n">
-        <v>6278314</v>
+        <v>6278302</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122126959</v>
+        <v>122126270</v>
       </c>
       <c r="B34" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5299,21 +5299,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491397</v>
+        <v>491452</v>
       </c>
       <c r="R34" t="n">
-        <v>6278316</v>
+        <v>6278297</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5367,22 +5367,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122126067</v>
+        <v>122126273</v>
       </c>
       <c r="B35" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5439,25 +5439,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491431</v>
+        <v>491430</v>
       </c>
       <c r="R35" t="n">
-        <v>6278305</v>
+        <v>6278304</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5511,22 +5511,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5571,10 +5571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122126270</v>
+        <v>122126068</v>
       </c>
       <c r="B36" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5583,25 +5583,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491452</v>
+        <v>491430</v>
       </c>
       <c r="R36" t="n">
-        <v>6278297</v>
+        <v>6278302</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5655,22 +5655,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5715,10 +5715,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122126960</v>
+        <v>122126301</v>
       </c>
       <c r="B37" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5731,21 +5731,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491399</v>
+        <v>491409</v>
       </c>
       <c r="R37" t="n">
-        <v>6278315</v>
+        <v>6278308</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5859,7 +5859,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122126066</v>
+        <v>122126067</v>
       </c>
       <c r="B38" t="n">
         <v>56266</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491433</v>
+        <v>491431</v>
       </c>
       <c r="R38" t="n">
         <v>6278305</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122126272</v>
+        <v>122126076</v>
       </c>
       <c r="B39" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491444</v>
+        <v>491469</v>
       </c>
       <c r="R39" t="n">
-        <v>6278302</v>
+        <v>6278289</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -6087,22 +6087,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6147,10 +6147,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122126147</v>
+        <v>122126960</v>
       </c>
       <c r="B40" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6159,25 +6159,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491403</v>
+        <v>491399</v>
       </c>
       <c r="R40" t="n">
-        <v>6278312</v>
+        <v>6278315</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -6231,22 +6231,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6291,7 +6291,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122126983</v>
+        <v>122126982</v>
       </c>
       <c r="B41" t="n">
         <v>56273</v>
@@ -6348,7 +6348,7 @@
         <v>491409</v>
       </c>
       <c r="R41" t="n">
-        <v>6278308</v>
+        <v>6278309</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6435,10 +6435,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122126146</v>
+        <v>122126961</v>
       </c>
       <c r="B42" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6447,25 +6447,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491408</v>
+        <v>491402</v>
       </c>
       <c r="R42" t="n">
-        <v>6278310</v>
+        <v>6278314</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6519,22 +6519,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6579,10 +6579,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122126064</v>
+        <v>122126971</v>
       </c>
       <c r="B43" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6591,25 +6591,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491433</v>
+        <v>491408</v>
       </c>
       <c r="R43" t="n">
-        <v>6278303</v>
+        <v>6278315</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6723,10 +6723,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122126062</v>
+        <v>122126294</v>
       </c>
       <c r="B44" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6735,25 +6735,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491432</v>
+        <v>491408</v>
       </c>
       <c r="R44" t="n">
-        <v>6278301</v>
+        <v>6278314</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6867,7 +6867,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122126059</v>
+        <v>122126147</v>
       </c>
       <c r="B45" t="n">
         <v>56266</v>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491410</v>
+        <v>491403</v>
       </c>
       <c r="R45" t="n">
-        <v>6278309</v>
+        <v>6278312</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6951,22 +6951,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7011,10 +7011,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122126068</v>
+        <v>122126985</v>
       </c>
       <c r="B46" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7023,25 +7023,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491430</v>
+        <v>491431</v>
       </c>
       <c r="R46" t="n">
-        <v>6278302</v>
+        <v>6278305</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122126985</v>
+        <v>122126295</v>
       </c>
       <c r="B47" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7171,21 +7171,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491431</v>
+        <v>491408</v>
       </c>
       <c r="R47" t="n">
-        <v>6278305</v>
+        <v>6278313</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122126305</v>
+        <v>122126059</v>
       </c>
       <c r="B48" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7311,25 +7311,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491431</v>
+        <v>491410</v>
       </c>
       <c r="R48" t="n">
-        <v>6278302</v>
+        <v>6278309</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7443,10 +7443,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122126081</v>
+        <v>122125949</v>
       </c>
       <c r="B49" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7455,25 +7455,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491467</v>
+        <v>491410</v>
       </c>
       <c r="R49" t="n">
-        <v>6278291</v>
+        <v>6278312</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -819,10 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126066</v>
+        <v>122126290</v>
       </c>
       <c r="B3" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,25 +831,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491433</v>
+        <v>491408</v>
       </c>
       <c r="R3" t="n">
-        <v>6278305</v>
+        <v>6278310</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126050</v>
+        <v>122126066</v>
       </c>
       <c r="B4" t="n">
         <v>56266</v>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491450</v>
+        <v>491433</v>
       </c>
       <c r="R4" t="n">
-        <v>6278297</v>
+        <v>6278305</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,22 +1047,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1107,7 +1107,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126064</v>
+        <v>122126050</v>
       </c>
       <c r="B5" t="n">
         <v>56266</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491433</v>
+        <v>491450</v>
       </c>
       <c r="R5" t="n">
-        <v>6278303</v>
+        <v>6278297</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1191,22 +1191,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1251,10 +1251,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126290</v>
+        <v>122126064</v>
       </c>
       <c r="B6" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491408</v>
+        <v>491433</v>
       </c>
       <c r="R6" t="n">
-        <v>6278310</v>
+        <v>6278303</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1971,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126082</v>
+        <v>122126983</v>
       </c>
       <c r="B11" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491466</v>
+        <v>491409</v>
       </c>
       <c r="R11" t="n">
-        <v>6278292</v>
+        <v>6278308</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122126983</v>
+        <v>122126293</v>
       </c>
       <c r="B12" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491409</v>
+        <v>491407</v>
       </c>
       <c r="R12" t="n">
-        <v>6278308</v>
+        <v>6278314</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2259,10 +2259,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122126293</v>
+        <v>122126082</v>
       </c>
       <c r="B13" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2271,25 +2271,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491407</v>
+        <v>491466</v>
       </c>
       <c r="R13" t="n">
-        <v>6278314</v>
+        <v>6278292</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -3699,7 +3699,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122126063</v>
+        <v>122126146</v>
       </c>
       <c r="B23" t="n">
         <v>56266</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491433</v>
+        <v>491408</v>
       </c>
       <c r="R23" t="n">
-        <v>6278302</v>
+        <v>6278310</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3783,22 +3783,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3843,7 +3843,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122126146</v>
+        <v>122126063</v>
       </c>
       <c r="B24" t="n">
         <v>56266</v>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491408</v>
+        <v>491433</v>
       </c>
       <c r="R24" t="n">
-        <v>6278310</v>
+        <v>6278302</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3927,22 +3927,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -7011,10 +7011,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122126985</v>
+        <v>122125949</v>
       </c>
       <c r="B46" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491431</v>
+        <v>491410</v>
       </c>
       <c r="R46" t="n">
-        <v>6278305</v>
+        <v>6278312</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122126295</v>
+        <v>122126985</v>
       </c>
       <c r="B47" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7171,21 +7171,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491408</v>
+        <v>491431</v>
       </c>
       <c r="R47" t="n">
-        <v>6278313</v>
+        <v>6278305</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122126059</v>
+        <v>122126295</v>
       </c>
       <c r="B48" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7311,25 +7311,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R48" t="n">
-        <v>6278309</v>
+        <v>6278313</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7443,10 +7443,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122125949</v>
+        <v>122126059</v>
       </c>
       <c r="B49" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7455,25 +7455,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7500,7 +7500,7 @@
         <v>491410</v>
       </c>
       <c r="R49" t="n">
-        <v>6278312</v>
+        <v>6278309</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126959</v>
+        <v>122126970</v>
       </c>
       <c r="B2" t="n">
         <v>56273</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491397</v>
+        <v>491409</v>
       </c>
       <c r="R2" t="n">
-        <v>6278316</v>
+        <v>6278314</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,7 +819,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126290</v>
+        <v>122126291</v>
       </c>
       <c r="B3" t="n">
         <v>56285</v>
@@ -963,7 +963,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126066</v>
+        <v>122126068</v>
       </c>
       <c r="B4" t="n">
         <v>56266</v>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491433</v>
+        <v>491430</v>
       </c>
       <c r="R4" t="n">
-        <v>6278305</v>
+        <v>6278302</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>23:25</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>23:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126050</v>
+        <v>122126298</v>
       </c>
       <c r="B5" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,25 +1119,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491450</v>
+        <v>491410</v>
       </c>
       <c r="R5" t="n">
-        <v>6278297</v>
+        <v>6278309</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1191,22 +1191,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1251,10 +1251,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126064</v>
+        <v>122126975</v>
       </c>
       <c r="B6" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491433</v>
+        <v>491407</v>
       </c>
       <c r="R6" t="n">
-        <v>6278303</v>
+        <v>6278313</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126144</v>
+        <v>122126305</v>
       </c>
       <c r="B7" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1407,25 +1407,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491449</v>
+        <v>491431</v>
       </c>
       <c r="R7" t="n">
-        <v>6278298</v>
+        <v>6278302</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1479,22 +1479,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1539,7 +1539,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126306</v>
+        <v>122126307</v>
       </c>
       <c r="B8" t="n">
         <v>56285</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126963</v>
+        <v>122126979</v>
       </c>
       <c r="B9" t="n">
         <v>56273</v>
@@ -1740,7 +1740,7 @@
         <v>491408</v>
       </c>
       <c r="R9" t="n">
-        <v>6278312</v>
+        <v>6278313</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122126974</v>
+        <v>122126146</v>
       </c>
       <c r="B10" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,25 +1839,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491407</v>
+        <v>491408</v>
       </c>
       <c r="R10" t="n">
-        <v>6278314</v>
+        <v>6278310</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1911,22 +1911,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1971,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126983</v>
+        <v>122126059</v>
       </c>
       <c r="B11" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491409</v>
+        <v>491410</v>
       </c>
       <c r="R11" t="n">
-        <v>6278308</v>
+        <v>6278309</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122126293</v>
+        <v>122126065</v>
       </c>
       <c r="B12" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491407</v>
+        <v>491433</v>
       </c>
       <c r="R12" t="n">
-        <v>6278314</v>
+        <v>6278303</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2259,10 +2259,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122126082</v>
+        <v>122126981</v>
       </c>
       <c r="B13" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2271,25 +2271,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491466</v>
+        <v>491408</v>
       </c>
       <c r="R13" t="n">
-        <v>6278292</v>
+        <v>6278312</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122126299</v>
+        <v>122126076</v>
       </c>
       <c r="B14" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2415,25 +2415,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491409</v>
+        <v>491469</v>
       </c>
       <c r="R14" t="n">
-        <v>6278309</v>
+        <v>6278289</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2547,10 +2547,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122126298</v>
+        <v>122126959</v>
       </c>
       <c r="B15" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491410</v>
+        <v>491397</v>
       </c>
       <c r="R15" t="n">
-        <v>6278309</v>
+        <v>6278316</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122126081</v>
+        <v>122126070</v>
       </c>
       <c r="B16" t="n">
         <v>56266</v>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491467</v>
+        <v>491431</v>
       </c>
       <c r="R16" t="n">
-        <v>6278291</v>
+        <v>6278302</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122126973</v>
+        <v>122126079</v>
       </c>
       <c r="B17" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2847,25 +2847,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491408</v>
+        <v>491470</v>
       </c>
       <c r="R17" t="n">
-        <v>6278314</v>
+        <v>6278289</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2979,10 +2979,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122126296</v>
+        <v>122126063</v>
       </c>
       <c r="B18" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2991,25 +2991,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491410</v>
+        <v>491433</v>
       </c>
       <c r="R18" t="n">
-        <v>6278308</v>
+        <v>6278302</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122126061</v>
+        <v>122126971</v>
       </c>
       <c r="B19" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3135,25 +3135,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R19" t="n">
-        <v>6278312</v>
+        <v>6278315</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3267,7 +3267,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122126969</v>
+        <v>122126976</v>
       </c>
       <c r="B20" t="n">
         <v>56273</v>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491409</v>
+        <v>491407</v>
       </c>
       <c r="R20" t="n">
         <v>6278314</v>
@@ -3356,17 +3356,17 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
+          <t>23:32</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
           <t>23:33</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>23:34</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3411,7 +3411,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122126975</v>
+        <v>122126973</v>
       </c>
       <c r="B21" t="n">
         <v>56273</v>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491407</v>
+        <v>491408</v>
       </c>
       <c r="R21" t="n">
-        <v>6278313</v>
+        <v>6278314</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122126272</v>
+        <v>122126067</v>
       </c>
       <c r="B22" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3567,25 +3567,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491444</v>
+        <v>491431</v>
       </c>
       <c r="R22" t="n">
-        <v>6278302</v>
+        <v>6278305</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3639,22 +3639,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122126146</v>
+        <v>122126270</v>
       </c>
       <c r="B23" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3711,25 +3711,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491408</v>
+        <v>491452</v>
       </c>
       <c r="R23" t="n">
-        <v>6278310</v>
+        <v>6278297</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3783,22 +3783,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122126063</v>
+        <v>122126294</v>
       </c>
       <c r="B24" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3855,25 +3855,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491433</v>
+        <v>491408</v>
       </c>
       <c r="R24" t="n">
-        <v>6278302</v>
+        <v>6278314</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3987,10 +3987,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122126079</v>
+        <v>122125948</v>
       </c>
       <c r="B25" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3999,25 +3999,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491470</v>
+        <v>491408</v>
       </c>
       <c r="R25" t="n">
-        <v>6278289</v>
+        <v>6278313</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4131,10 +4131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122126073</v>
+        <v>122125950</v>
       </c>
       <c r="B26" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4143,25 +4143,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491432</v>
+        <v>491430</v>
       </c>
       <c r="R26" t="n">
-        <v>6278302</v>
+        <v>6278303</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4275,10 +4275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122125948</v>
+        <v>122126050</v>
       </c>
       <c r="B27" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4287,25 +4287,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491408</v>
+        <v>491450</v>
       </c>
       <c r="R27" t="n">
-        <v>6278313</v>
+        <v>6278297</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4359,22 +4359,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122126062</v>
+        <v>122125949</v>
       </c>
       <c r="B28" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491432</v>
+        <v>491410</v>
       </c>
       <c r="R28" t="n">
-        <v>6278301</v>
+        <v>6278312</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4563,10 +4563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126060</v>
+        <v>122126961</v>
       </c>
       <c r="B29" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4575,25 +4575,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491410</v>
+        <v>491402</v>
       </c>
       <c r="R29" t="n">
-        <v>6278308</v>
+        <v>6278314</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4707,7 +4707,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122126978</v>
+        <v>122126984</v>
       </c>
       <c r="B30" t="n">
         <v>56273</v>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R30" t="n">
-        <v>6278313</v>
+        <v>6278308</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4851,7 +4851,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126069</v>
+        <v>122126147</v>
       </c>
       <c r="B31" t="n">
         <v>56266</v>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491431</v>
+        <v>491403</v>
       </c>
       <c r="R31" t="n">
-        <v>6278302</v>
+        <v>6278312</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4935,22 +4935,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4995,10 +4995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122125950</v>
+        <v>122126062</v>
       </c>
       <c r="B32" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5007,25 +5007,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491430</v>
+        <v>491432</v>
       </c>
       <c r="R32" t="n">
-        <v>6278303</v>
+        <v>6278301</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5139,10 +5139,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122126305</v>
+        <v>122126985</v>
       </c>
       <c r="B33" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5155,21 +5155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -5196,7 +5196,7 @@
         <v>491431</v>
       </c>
       <c r="R33" t="n">
-        <v>6278302</v>
+        <v>6278305</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122126270</v>
+        <v>122126060</v>
       </c>
       <c r="B34" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5295,25 +5295,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491452</v>
+        <v>491410</v>
       </c>
       <c r="R34" t="n">
-        <v>6278297</v>
+        <v>6278308</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5367,22 +5367,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122126273</v>
+        <v>122126144</v>
       </c>
       <c r="B35" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5439,25 +5439,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491430</v>
+        <v>491449</v>
       </c>
       <c r="R35" t="n">
-        <v>6278304</v>
+        <v>6278298</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5511,22 +5511,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5571,10 +5571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122126068</v>
+        <v>122126273</v>
       </c>
       <c r="B36" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5583,25 +5583,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5628,7 +5628,7 @@
         <v>491430</v>
       </c>
       <c r="R36" t="n">
-        <v>6278302</v>
+        <v>6278304</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5655,22 +5655,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5715,10 +5715,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122126301</v>
+        <v>122126066</v>
       </c>
       <c r="B37" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5727,25 +5727,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491409</v>
+        <v>491433</v>
       </c>
       <c r="R37" t="n">
-        <v>6278308</v>
+        <v>6278305</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5859,10 +5859,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122126067</v>
+        <v>122126296</v>
       </c>
       <c r="B38" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5871,25 +5871,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491431</v>
+        <v>491410</v>
       </c>
       <c r="R38" t="n">
-        <v>6278305</v>
+        <v>6278308</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6003,10 +6003,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122126076</v>
+        <v>122126960</v>
       </c>
       <c r="B39" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491469</v>
+        <v>491399</v>
       </c>
       <c r="R39" t="n">
-        <v>6278289</v>
+        <v>6278315</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6147,10 +6147,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122126960</v>
+        <v>122126272</v>
       </c>
       <c r="B40" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6163,21 +6163,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491399</v>
+        <v>491444</v>
       </c>
       <c r="R40" t="n">
-        <v>6278315</v>
+        <v>6278302</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -6231,22 +6231,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122126982</v>
+        <v>122126073</v>
       </c>
       <c r="B41" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6303,25 +6303,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491409</v>
+        <v>491432</v>
       </c>
       <c r="R41" t="n">
-        <v>6278309</v>
+        <v>6278302</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6435,10 +6435,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122126961</v>
+        <v>122126081</v>
       </c>
       <c r="B42" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6447,25 +6447,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491402</v>
+        <v>491467</v>
       </c>
       <c r="R42" t="n">
-        <v>6278314</v>
+        <v>6278291</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6579,10 +6579,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122126971</v>
+        <v>122126299</v>
       </c>
       <c r="B43" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6595,21 +6595,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R43" t="n">
-        <v>6278315</v>
+        <v>6278309</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6668,17 +6668,17 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
           <t>23:32</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>23:33</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6723,7 +6723,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122126294</v>
+        <v>122126295</v>
       </c>
       <c r="B44" t="n">
         <v>56285</v>
@@ -6780,7 +6780,7 @@
         <v>491408</v>
       </c>
       <c r="R44" t="n">
-        <v>6278314</v>
+        <v>6278313</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122126147</v>
+        <v>122126982</v>
       </c>
       <c r="B45" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6879,25 +6879,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491403</v>
+        <v>491409</v>
       </c>
       <c r="R45" t="n">
-        <v>6278312</v>
+        <v>6278309</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6951,22 +6951,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7011,10 +7011,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122125949</v>
+        <v>122126061</v>
       </c>
       <c r="B46" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7023,25 +7023,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122126985</v>
+        <v>122126082</v>
       </c>
       <c r="B47" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7167,25 +7167,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491431</v>
+        <v>491466</v>
       </c>
       <c r="R47" t="n">
-        <v>6278305</v>
+        <v>6278292</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7299,7 +7299,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122126295</v>
+        <v>122126293</v>
       </c>
       <c r="B48" t="n">
         <v>56285</v>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491408</v>
+        <v>491407</v>
       </c>
       <c r="R48" t="n">
-        <v>6278313</v>
+        <v>6278314</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -7443,10 +7443,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122126059</v>
+        <v>122126302</v>
       </c>
       <c r="B49" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7455,25 +7455,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491410</v>
+        <v>491409</v>
       </c>
       <c r="R49" t="n">
-        <v>6278309</v>
+        <v>6278308</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7532,17 +7532,17 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
           <t>23:31</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>23:32</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126970</v>
+        <v>122126062</v>
       </c>
       <c r="B2" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491409</v>
+        <v>491432</v>
       </c>
       <c r="R2" t="n">
-        <v>6278314</v>
+        <v>6278301</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,7 +819,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126291</v>
+        <v>122126300</v>
       </c>
       <c r="B3" t="n">
         <v>56285</v>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R3" t="n">
-        <v>6278310</v>
+        <v>6278309</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,10 +963,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126068</v>
+        <v>122126971</v>
       </c>
       <c r="B4" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,25 +975,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491430</v>
+        <v>491408</v>
       </c>
       <c r="R4" t="n">
-        <v>6278302</v>
+        <v>6278315</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126298</v>
+        <v>122126983</v>
       </c>
       <c r="B5" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491410</v>
+        <v>491409</v>
       </c>
       <c r="R5" t="n">
-        <v>6278309</v>
+        <v>6278308</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>23:31</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>23:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1251,10 +1251,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126975</v>
+        <v>122126070</v>
       </c>
       <c r="B6" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491407</v>
+        <v>491431</v>
       </c>
       <c r="R6" t="n">
-        <v>6278313</v>
+        <v>6278302</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1395,7 +1395,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126305</v>
+        <v>122126291</v>
       </c>
       <c r="B7" t="n">
         <v>56285</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491431</v>
+        <v>491408</v>
       </c>
       <c r="R7" t="n">
-        <v>6278302</v>
+        <v>6278310</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126307</v>
+        <v>122126959</v>
       </c>
       <c r="B8" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491432</v>
+        <v>491397</v>
       </c>
       <c r="R8" t="n">
-        <v>6278301</v>
+        <v>6278316</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126979</v>
+        <v>122126976</v>
       </c>
       <c r="B9" t="n">
         <v>56273</v>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491408</v>
+        <v>491407</v>
       </c>
       <c r="R9" t="n">
-        <v>6278313</v>
+        <v>6278314</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122126146</v>
+        <v>122125947</v>
       </c>
       <c r="B10" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,25 +1839,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1884,7 +1884,7 @@
         <v>491408</v>
       </c>
       <c r="R10" t="n">
-        <v>6278310</v>
+        <v>6278313</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1911,22 +1911,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1971,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126059</v>
+        <v>122126960</v>
       </c>
       <c r="B11" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491410</v>
+        <v>491399</v>
       </c>
       <c r="R11" t="n">
-        <v>6278309</v>
+        <v>6278315</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122126065</v>
+        <v>122126967</v>
       </c>
       <c r="B12" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491433</v>
+        <v>491408</v>
       </c>
       <c r="R12" t="n">
-        <v>6278303</v>
+        <v>6278312</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2259,10 +2259,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122126981</v>
+        <v>122126072</v>
       </c>
       <c r="B13" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2271,25 +2271,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491408</v>
+        <v>491432</v>
       </c>
       <c r="R13" t="n">
-        <v>6278312</v>
+        <v>6278302</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2403,7 +2403,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122126076</v>
+        <v>122126068</v>
       </c>
       <c r="B14" t="n">
         <v>56266</v>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491469</v>
+        <v>491430</v>
       </c>
       <c r="R14" t="n">
-        <v>6278289</v>
+        <v>6278302</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2547,7 +2547,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122126959</v>
+        <v>122126979</v>
       </c>
       <c r="B15" t="n">
         <v>56273</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491397</v>
+        <v>491408</v>
       </c>
       <c r="R15" t="n">
-        <v>6278316</v>
+        <v>6278313</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122126070</v>
+        <v>122126146</v>
       </c>
       <c r="B16" t="n">
         <v>56266</v>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491431</v>
+        <v>491408</v>
       </c>
       <c r="R16" t="n">
-        <v>6278302</v>
+        <v>6278310</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2775,22 +2775,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2835,7 +2835,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122126079</v>
+        <v>122126060</v>
       </c>
       <c r="B17" t="n">
         <v>56266</v>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491470</v>
+        <v>491410</v>
       </c>
       <c r="R17" t="n">
-        <v>6278289</v>
+        <v>6278308</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2979,7 +2979,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122126063</v>
+        <v>122126082</v>
       </c>
       <c r="B18" t="n">
         <v>56266</v>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491433</v>
+        <v>491466</v>
       </c>
       <c r="R18" t="n">
-        <v>6278302</v>
+        <v>6278292</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122126971</v>
+        <v>122126296</v>
       </c>
       <c r="B19" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491408</v>
+        <v>491410</v>
       </c>
       <c r="R19" t="n">
-        <v>6278315</v>
+        <v>6278308</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3212,17 +3212,17 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>23:32</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>23:33</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3267,10 +3267,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122126976</v>
+        <v>122126307</v>
       </c>
       <c r="B20" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491407</v>
+        <v>491432</v>
       </c>
       <c r="R20" t="n">
-        <v>6278314</v>
+        <v>6278301</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3411,10 +3411,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122126973</v>
+        <v>122126066</v>
       </c>
       <c r="B21" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3423,25 +3423,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491408</v>
+        <v>491433</v>
       </c>
       <c r="R21" t="n">
-        <v>6278314</v>
+        <v>6278305</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122126067</v>
+        <v>122126973</v>
       </c>
       <c r="B22" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3567,25 +3567,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491431</v>
+        <v>491408</v>
       </c>
       <c r="R22" t="n">
-        <v>6278305</v>
+        <v>6278314</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122126270</v>
+        <v>122125949</v>
       </c>
       <c r="B23" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491452</v>
+        <v>491410</v>
       </c>
       <c r="R23" t="n">
-        <v>6278297</v>
+        <v>6278312</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3783,22 +3783,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3843,7 +3843,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122126294</v>
+        <v>122126305</v>
       </c>
       <c r="B24" t="n">
         <v>56285</v>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491408</v>
+        <v>491431</v>
       </c>
       <c r="R24" t="n">
-        <v>6278314</v>
+        <v>6278302</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3987,10 +3987,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122125948</v>
+        <v>122126295</v>
       </c>
       <c r="B25" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4003,21 +4003,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4131,10 +4131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122125950</v>
+        <v>122126975</v>
       </c>
       <c r="B26" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4147,21 +4147,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491430</v>
+        <v>491407</v>
       </c>
       <c r="R26" t="n">
-        <v>6278303</v>
+        <v>6278313</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4275,7 +4275,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122126050</v>
+        <v>122126076</v>
       </c>
       <c r="B27" t="n">
         <v>56266</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491450</v>
+        <v>491469</v>
       </c>
       <c r="R27" t="n">
-        <v>6278297</v>
+        <v>6278289</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4359,22 +4359,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122125949</v>
+        <v>122126144</v>
       </c>
       <c r="B28" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491410</v>
+        <v>491449</v>
       </c>
       <c r="R28" t="n">
-        <v>6278312</v>
+        <v>6278298</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4563,7 +4563,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126961</v>
+        <v>122126982</v>
       </c>
       <c r="B29" t="n">
         <v>56273</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491402</v>
+        <v>491409</v>
       </c>
       <c r="R29" t="n">
-        <v>6278314</v>
+        <v>6278309</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4707,7 +4707,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122126984</v>
+        <v>122126970</v>
       </c>
       <c r="B30" t="n">
         <v>56273</v>
@@ -4764,7 +4764,7 @@
         <v>491409</v>
       </c>
       <c r="R30" t="n">
-        <v>6278308</v>
+        <v>6278314</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4851,7 +4851,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126147</v>
+        <v>122126081</v>
       </c>
       <c r="B31" t="n">
         <v>56266</v>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491403</v>
+        <v>491467</v>
       </c>
       <c r="R31" t="n">
-        <v>6278312</v>
+        <v>6278291</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4935,22 +4935,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4995,10 +4995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122126062</v>
+        <v>122126985</v>
       </c>
       <c r="B32" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5007,25 +5007,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491432</v>
+        <v>491431</v>
       </c>
       <c r="R32" t="n">
-        <v>6278301</v>
+        <v>6278305</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5139,10 +5139,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122126985</v>
+        <v>122126303</v>
       </c>
       <c r="B33" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5155,21 +5155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491431</v>
+        <v>491410</v>
       </c>
       <c r="R33" t="n">
-        <v>6278305</v>
+        <v>6278309</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5283,7 +5283,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122126060</v>
+        <v>122126050</v>
       </c>
       <c r="B34" t="n">
         <v>56266</v>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491410</v>
+        <v>491450</v>
       </c>
       <c r="R34" t="n">
-        <v>6278308</v>
+        <v>6278297</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5367,22 +5367,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122126144</v>
+        <v>122126270</v>
       </c>
       <c r="B35" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5439,25 +5439,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491449</v>
+        <v>491452</v>
       </c>
       <c r="R35" t="n">
-        <v>6278298</v>
+        <v>6278297</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5511,22 +5511,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5571,10 +5571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122126273</v>
+        <v>122126079</v>
       </c>
       <c r="B36" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5583,25 +5583,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491430</v>
+        <v>491470</v>
       </c>
       <c r="R36" t="n">
-        <v>6278304</v>
+        <v>6278289</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5655,22 +5655,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5715,7 +5715,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122126066</v>
+        <v>122126064</v>
       </c>
       <c r="B37" t="n">
         <v>56266</v>
@@ -5772,7 +5772,7 @@
         <v>491433</v>
       </c>
       <c r="R37" t="n">
-        <v>6278305</v>
+        <v>6278303</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5859,10 +5859,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122126296</v>
+        <v>122126061</v>
       </c>
       <c r="B38" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5871,25 +5871,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5916,7 +5916,7 @@
         <v>491410</v>
       </c>
       <c r="R38" t="n">
-        <v>6278308</v>
+        <v>6278312</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6003,10 +6003,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122126960</v>
+        <v>122126059</v>
       </c>
       <c r="B39" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491399</v>
+        <v>491410</v>
       </c>
       <c r="R39" t="n">
-        <v>6278315</v>
+        <v>6278309</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6147,7 +6147,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122126272</v>
+        <v>122126294</v>
       </c>
       <c r="B40" t="n">
         <v>56285</v>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491444</v>
+        <v>491408</v>
       </c>
       <c r="R40" t="n">
-        <v>6278302</v>
+        <v>6278314</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -6231,22 +6231,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122126073</v>
+        <v>122126273</v>
       </c>
       <c r="B41" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6303,25 +6303,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491432</v>
+        <v>491430</v>
       </c>
       <c r="R41" t="n">
-        <v>6278302</v>
+        <v>6278304</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6375,22 +6375,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6435,10 +6435,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122126081</v>
+        <v>122125950</v>
       </c>
       <c r="B42" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6447,25 +6447,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491467</v>
+        <v>491430</v>
       </c>
       <c r="R42" t="n">
-        <v>6278291</v>
+        <v>6278303</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6579,10 +6579,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122126299</v>
+        <v>122126067</v>
       </c>
       <c r="B43" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6591,25 +6591,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491409</v>
+        <v>491431</v>
       </c>
       <c r="R43" t="n">
-        <v>6278309</v>
+        <v>6278305</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6723,10 +6723,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122126295</v>
+        <v>122126147</v>
       </c>
       <c r="B44" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6735,25 +6735,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491408</v>
+        <v>491403</v>
       </c>
       <c r="R44" t="n">
-        <v>6278313</v>
+        <v>6278312</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6807,22 +6807,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6867,10 +6867,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122126982</v>
+        <v>122126063</v>
       </c>
       <c r="B45" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6879,25 +6879,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491409</v>
+        <v>491433</v>
       </c>
       <c r="R45" t="n">
-        <v>6278309</v>
+        <v>6278302</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7011,10 +7011,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122126061</v>
+        <v>122126302</v>
       </c>
       <c r="B46" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7023,25 +7023,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491410</v>
+        <v>491409</v>
       </c>
       <c r="R46" t="n">
-        <v>6278312</v>
+        <v>6278308</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122126082</v>
+        <v>122126293</v>
       </c>
       <c r="B47" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7167,25 +7167,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491466</v>
+        <v>491407</v>
       </c>
       <c r="R47" t="n">
-        <v>6278292</v>
+        <v>6278314</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7299,7 +7299,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122126293</v>
+        <v>122126272</v>
       </c>
       <c r="B48" t="n">
         <v>56285</v>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491407</v>
+        <v>491444</v>
       </c>
       <c r="R48" t="n">
-        <v>6278314</v>
+        <v>6278302</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -7383,22 +7383,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7443,10 +7443,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122126302</v>
+        <v>122126961</v>
       </c>
       <c r="B49" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7459,21 +7459,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491409</v>
+        <v>491402</v>
       </c>
       <c r="R49" t="n">
-        <v>6278308</v>
+        <v>6278314</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -819,10 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126300</v>
+        <v>122126971</v>
       </c>
       <c r="B3" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,21 +835,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491409</v>
+        <v>491408</v>
       </c>
       <c r="R3" t="n">
-        <v>6278309</v>
+        <v>6278315</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126971</v>
+        <v>122126983</v>
       </c>
       <c r="B4" t="n">
         <v>56273</v>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R4" t="n">
-        <v>6278315</v>
+        <v>6278308</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126983</v>
+        <v>122126300</v>
       </c>
       <c r="B5" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1164,7 +1164,7 @@
         <v>491409</v>
       </c>
       <c r="R5" t="n">
-        <v>6278308</v>
+        <v>6278309</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126291</v>
+        <v>122126959</v>
       </c>
       <c r="B7" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491408</v>
+        <v>491397</v>
       </c>
       <c r="R7" t="n">
-        <v>6278310</v>
+        <v>6278316</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126959</v>
+        <v>122126291</v>
       </c>
       <c r="B8" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491397</v>
+        <v>491408</v>
       </c>
       <c r="R8" t="n">
-        <v>6278316</v>
+        <v>6278310</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1628,17 +1628,17 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>23:35</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>23:36</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1971,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126960</v>
+        <v>122126072</v>
       </c>
       <c r="B11" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491399</v>
+        <v>491432</v>
       </c>
       <c r="R11" t="n">
-        <v>6278315</v>
+        <v>6278302</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122126967</v>
+        <v>122126068</v>
       </c>
       <c r="B12" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491408</v>
+        <v>491430</v>
       </c>
       <c r="R12" t="n">
-        <v>6278312</v>
+        <v>6278302</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2259,10 +2259,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122126072</v>
+        <v>122126960</v>
       </c>
       <c r="B13" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2271,25 +2271,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491432</v>
+        <v>491399</v>
       </c>
       <c r="R13" t="n">
-        <v>6278302</v>
+        <v>6278315</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122126068</v>
+        <v>122126967</v>
       </c>
       <c r="B14" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2415,25 +2415,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491430</v>
+        <v>491408</v>
       </c>
       <c r="R14" t="n">
-        <v>6278302</v>
+        <v>6278312</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2547,10 +2547,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122126979</v>
+        <v>122126146</v>
       </c>
       <c r="B15" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2559,25 +2559,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2604,7 +2604,7 @@
         <v>491408</v>
       </c>
       <c r="R15" t="n">
-        <v>6278313</v>
+        <v>6278310</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2631,22 +2631,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122126146</v>
+        <v>122126060</v>
       </c>
       <c r="B16" t="n">
         <v>56266</v>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491408</v>
+        <v>491410</v>
       </c>
       <c r="R16" t="n">
-        <v>6278310</v>
+        <v>6278308</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2775,22 +2775,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122126060</v>
+        <v>122126979</v>
       </c>
       <c r="B17" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2847,25 +2847,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R17" t="n">
-        <v>6278308</v>
+        <v>6278313</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126062</v>
+        <v>122126976</v>
       </c>
       <c r="B2" t="n">
-        <v>56266</v>
+        <v>56278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491432</v>
+        <v>491407</v>
       </c>
       <c r="R2" t="n">
-        <v>6278301</v>
+        <v>6278314</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,10 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126971</v>
+        <v>122126970</v>
       </c>
       <c r="B3" t="n">
-        <v>56273</v>
+        <v>56278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R3" t="n">
-        <v>6278315</v>
+        <v>6278314</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,10 +963,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126983</v>
+        <v>122126147</v>
       </c>
       <c r="B4" t="n">
-        <v>56273</v>
+        <v>56271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,25 +975,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491409</v>
+        <v>491403</v>
       </c>
       <c r="R4" t="n">
-        <v>6278308</v>
+        <v>6278312</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,22 +1047,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126300</v>
+        <v>122126069</v>
       </c>
       <c r="B5" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,25 +1119,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491409</v>
+        <v>491431</v>
       </c>
       <c r="R5" t="n">
-        <v>6278309</v>
+        <v>6278302</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1251,10 +1251,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126070</v>
+        <v>122126063</v>
       </c>
       <c r="B6" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491431</v>
+        <v>491433</v>
       </c>
       <c r="R6" t="n">
         <v>6278302</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126959</v>
+        <v>122126303</v>
       </c>
       <c r="B7" t="n">
-        <v>56273</v>
+        <v>56290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491397</v>
+        <v>491410</v>
       </c>
       <c r="R7" t="n">
-        <v>6278316</v>
+        <v>6278309</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1542,7 +1542,7 @@
         <v>122126291</v>
       </c>
       <c r="B8" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126976</v>
+        <v>122126959</v>
       </c>
       <c r="B9" t="n">
-        <v>56273</v>
+        <v>56278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491407</v>
+        <v>491397</v>
       </c>
       <c r="R9" t="n">
-        <v>6278314</v>
+        <v>6278316</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122125947</v>
+        <v>122126273</v>
       </c>
       <c r="B10" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491408</v>
+        <v>491430</v>
       </c>
       <c r="R10" t="n">
-        <v>6278313</v>
+        <v>6278304</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1911,22 +1911,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1971,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126072</v>
+        <v>122126060</v>
       </c>
       <c r="B11" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491432</v>
+        <v>491410</v>
       </c>
       <c r="R11" t="n">
-        <v>6278302</v>
+        <v>6278308</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122126068</v>
+        <v>122126294</v>
       </c>
       <c r="B12" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491430</v>
+        <v>491408</v>
       </c>
       <c r="R12" t="n">
-        <v>6278302</v>
+        <v>6278314</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2259,10 +2259,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122126960</v>
+        <v>122126300</v>
       </c>
       <c r="B13" t="n">
-        <v>56273</v>
+        <v>56290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491399</v>
+        <v>491409</v>
       </c>
       <c r="R13" t="n">
-        <v>6278315</v>
+        <v>6278309</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122126967</v>
+        <v>122126302</v>
       </c>
       <c r="B14" t="n">
-        <v>56273</v>
+        <v>56290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2419,21 +2419,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R14" t="n">
-        <v>6278312</v>
+        <v>6278308</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2547,10 +2547,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122126146</v>
+        <v>122126307</v>
       </c>
       <c r="B15" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2559,25 +2559,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491408</v>
+        <v>491432</v>
       </c>
       <c r="R15" t="n">
-        <v>6278310</v>
+        <v>6278301</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2631,22 +2631,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122126060</v>
+        <v>122126066</v>
       </c>
       <c r="B16" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491410</v>
+        <v>491433</v>
       </c>
       <c r="R16" t="n">
-        <v>6278308</v>
+        <v>6278305</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122126979</v>
+        <v>122126072</v>
       </c>
       <c r="B17" t="n">
-        <v>56273</v>
+        <v>56271</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2847,25 +2847,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491408</v>
+        <v>491432</v>
       </c>
       <c r="R17" t="n">
-        <v>6278313</v>
+        <v>6278302</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2979,10 +2979,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122126082</v>
+        <v>122126081</v>
       </c>
       <c r="B18" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491466</v>
+        <v>491467</v>
       </c>
       <c r="R18" t="n">
-        <v>6278292</v>
+        <v>6278291</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122126296</v>
+        <v>122126082</v>
       </c>
       <c r="B19" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3135,25 +3135,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491410</v>
+        <v>491466</v>
       </c>
       <c r="R19" t="n">
-        <v>6278308</v>
+        <v>6278292</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3267,7 +3267,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122126307</v>
+        <v>122125948</v>
       </c>
       <c r="B20" t="n">
         <v>56285</v>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491432</v>
+        <v>491408</v>
       </c>
       <c r="R20" t="n">
-        <v>6278301</v>
+        <v>6278313</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3411,10 +3411,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122126066</v>
+        <v>122126978</v>
       </c>
       <c r="B21" t="n">
-        <v>56266</v>
+        <v>56278</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3423,25 +3423,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491433</v>
+        <v>491408</v>
       </c>
       <c r="R21" t="n">
-        <v>6278305</v>
+        <v>6278313</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122126973</v>
+        <v>122126962</v>
       </c>
       <c r="B22" t="n">
-        <v>56273</v>
+        <v>56278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>491408</v>
       </c>
       <c r="R22" t="n">
-        <v>6278314</v>
+        <v>6278312</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122125949</v>
+        <v>122126971</v>
       </c>
       <c r="B23" t="n">
-        <v>56280</v>
+        <v>56278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R23" t="n">
-        <v>6278312</v>
+        <v>6278315</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122126305</v>
+        <v>122126076</v>
       </c>
       <c r="B24" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3855,25 +3855,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491431</v>
+        <v>491469</v>
       </c>
       <c r="R24" t="n">
-        <v>6278302</v>
+        <v>6278289</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3987,10 +3987,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122126295</v>
+        <v>122126067</v>
       </c>
       <c r="B25" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3999,25 +3999,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491408</v>
+        <v>491431</v>
       </c>
       <c r="R25" t="n">
-        <v>6278313</v>
+        <v>6278305</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4131,10 +4131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122126975</v>
+        <v>122126065</v>
       </c>
       <c r="B26" t="n">
-        <v>56273</v>
+        <v>56271</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4143,25 +4143,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491407</v>
+        <v>491433</v>
       </c>
       <c r="R26" t="n">
-        <v>6278313</v>
+        <v>6278303</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4275,10 +4275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122126076</v>
+        <v>122126961</v>
       </c>
       <c r="B27" t="n">
-        <v>56266</v>
+        <v>56278</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4287,25 +4287,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491469</v>
+        <v>491402</v>
       </c>
       <c r="R27" t="n">
-        <v>6278289</v>
+        <v>6278314</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122126144</v>
+        <v>122126297</v>
       </c>
       <c r="B28" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491449</v>
+        <v>491410</v>
       </c>
       <c r="R28" t="n">
-        <v>6278298</v>
+        <v>6278308</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4563,10 +4563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126982</v>
+        <v>122126295</v>
       </c>
       <c r="B29" t="n">
-        <v>56273</v>
+        <v>56290</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4579,21 +4579,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491409</v>
+        <v>491408</v>
       </c>
       <c r="R29" t="n">
-        <v>6278309</v>
+        <v>6278313</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4707,10 +4707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122126970</v>
+        <v>122126983</v>
       </c>
       <c r="B30" t="n">
-        <v>56273</v>
+        <v>56278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>491409</v>
       </c>
       <c r="R30" t="n">
-        <v>6278314</v>
+        <v>6278308</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4851,10 +4851,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126081</v>
+        <v>122126975</v>
       </c>
       <c r="B31" t="n">
-        <v>56266</v>
+        <v>56278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4863,25 +4863,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491467</v>
+        <v>491407</v>
       </c>
       <c r="R31" t="n">
-        <v>6278291</v>
+        <v>6278313</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4995,10 +4995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122126985</v>
+        <v>122126960</v>
       </c>
       <c r="B32" t="n">
-        <v>56273</v>
+        <v>56278</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491431</v>
+        <v>491399</v>
       </c>
       <c r="R32" t="n">
-        <v>6278305</v>
+        <v>6278315</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5139,10 +5139,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122126303</v>
+        <v>122126985</v>
       </c>
       <c r="B33" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5155,21 +5155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491410</v>
+        <v>491431</v>
       </c>
       <c r="R33" t="n">
-        <v>6278309</v>
+        <v>6278305</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122126050</v>
+        <v>122126062</v>
       </c>
       <c r="B34" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491450</v>
+        <v>491432</v>
       </c>
       <c r="R34" t="n">
-        <v>6278297</v>
+        <v>6278301</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5367,22 +5367,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122126270</v>
+        <v>122126050</v>
       </c>
       <c r="B35" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5439,25 +5439,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491452</v>
+        <v>491450</v>
       </c>
       <c r="R35" t="n">
         <v>6278297</v>
@@ -5516,17 +5516,17 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
           <t>00:16</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:17</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5571,10 +5571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122126079</v>
+        <v>122126972</v>
       </c>
       <c r="B36" t="n">
-        <v>56266</v>
+        <v>56278</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5583,25 +5583,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491470</v>
+        <v>491408</v>
       </c>
       <c r="R36" t="n">
-        <v>6278289</v>
+        <v>6278314</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5715,10 +5715,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122126064</v>
+        <v>122126305</v>
       </c>
       <c r="B37" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5727,25 +5727,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491433</v>
+        <v>491431</v>
       </c>
       <c r="R37" t="n">
-        <v>6278303</v>
+        <v>6278302</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5859,10 +5859,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122126061</v>
+        <v>122126079</v>
       </c>
       <c r="B38" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491410</v>
+        <v>491470</v>
       </c>
       <c r="R38" t="n">
-        <v>6278312</v>
+        <v>6278289</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6003,10 +6003,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122126059</v>
+        <v>122126144</v>
       </c>
       <c r="B39" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491410</v>
+        <v>491449</v>
       </c>
       <c r="R39" t="n">
-        <v>6278309</v>
+        <v>6278298</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -6087,22 +6087,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6147,10 +6147,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122126294</v>
+        <v>122126068</v>
       </c>
       <c r="B40" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6159,25 +6159,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491408</v>
+        <v>491430</v>
       </c>
       <c r="R40" t="n">
-        <v>6278314</v>
+        <v>6278302</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122126273</v>
+        <v>122126982</v>
       </c>
       <c r="B41" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6307,21 +6307,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491430</v>
+        <v>491409</v>
       </c>
       <c r="R41" t="n">
-        <v>6278304</v>
+        <v>6278309</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6375,22 +6375,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6435,10 +6435,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122125950</v>
+        <v>122126146</v>
       </c>
       <c r="B42" t="n">
-        <v>56280</v>
+        <v>56271</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6447,25 +6447,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491430</v>
+        <v>491408</v>
       </c>
       <c r="R42" t="n">
-        <v>6278303</v>
+        <v>6278310</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6519,22 +6519,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6579,10 +6579,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122126067</v>
+        <v>122126293</v>
       </c>
       <c r="B43" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6591,25 +6591,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491431</v>
+        <v>491407</v>
       </c>
       <c r="R43" t="n">
-        <v>6278305</v>
+        <v>6278314</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6723,10 +6723,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122126147</v>
+        <v>122126271</v>
       </c>
       <c r="B44" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6735,25 +6735,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491403</v>
+        <v>491452</v>
       </c>
       <c r="R44" t="n">
-        <v>6278312</v>
+        <v>6278297</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6807,22 +6807,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6867,10 +6867,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122126063</v>
+        <v>122126272</v>
       </c>
       <c r="B45" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6879,25 +6879,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491433</v>
+        <v>491444</v>
       </c>
       <c r="R45" t="n">
         <v>6278302</v>
@@ -6951,22 +6951,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7011,7 +7011,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122126302</v>
+        <v>122125950</v>
       </c>
       <c r="B46" t="n">
         <v>56285</v>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491409</v>
+        <v>491430</v>
       </c>
       <c r="R46" t="n">
-        <v>6278308</v>
+        <v>6278303</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122126293</v>
+        <v>122126059</v>
       </c>
       <c r="B47" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7167,25 +7167,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491407</v>
+        <v>491410</v>
       </c>
       <c r="R47" t="n">
-        <v>6278314</v>
+        <v>6278309</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -7244,17 +7244,17 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
           <t>23:32</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>23:33</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122126272</v>
+        <v>122126061</v>
       </c>
       <c r="B48" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7311,25 +7311,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491444</v>
+        <v>491410</v>
       </c>
       <c r="R48" t="n">
-        <v>6278302</v>
+        <v>6278312</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -7383,22 +7383,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7443,10 +7443,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122126961</v>
+        <v>122125949</v>
       </c>
       <c r="B49" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7459,21 +7459,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491402</v>
+        <v>491410</v>
       </c>
       <c r="R49" t="n">
-        <v>6278314</v>
+        <v>6278312</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126976</v>
+        <v>122126076</v>
       </c>
       <c r="B2" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491407</v>
+        <v>491469</v>
       </c>
       <c r="R2" t="n">
-        <v>6278314</v>
+        <v>6278289</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,10 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126970</v>
+        <v>122126050</v>
       </c>
       <c r="B3" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,25 +831,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491409</v>
+        <v>491450</v>
       </c>
       <c r="R3" t="n">
-        <v>6278314</v>
+        <v>6278297</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,22 +903,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,10 +963,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126147</v>
+        <v>122126303</v>
       </c>
       <c r="B4" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,25 +975,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491403</v>
+        <v>491410</v>
       </c>
       <c r="R4" t="n">
-        <v>6278312</v>
+        <v>6278309</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,22 +1047,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126069</v>
+        <v>122126272</v>
       </c>
       <c r="B5" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,25 +1119,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491431</v>
+        <v>491444</v>
       </c>
       <c r="R5" t="n">
         <v>6278302</v>
@@ -1191,22 +1191,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1251,10 +1251,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126063</v>
+        <v>122126294</v>
       </c>
       <c r="B6" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491433</v>
+        <v>491408</v>
       </c>
       <c r="R6" t="n">
-        <v>6278302</v>
+        <v>6278314</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126303</v>
+        <v>122126965</v>
       </c>
       <c r="B7" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R7" t="n">
-        <v>6278309</v>
+        <v>6278313</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126291</v>
+        <v>122126072</v>
       </c>
       <c r="B8" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1551,25 +1551,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491408</v>
+        <v>491432</v>
       </c>
       <c r="R8" t="n">
-        <v>6278310</v>
+        <v>6278302</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126959</v>
+        <v>122126062</v>
       </c>
       <c r="B9" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491397</v>
+        <v>491432</v>
       </c>
       <c r="R9" t="n">
-        <v>6278316</v>
+        <v>6278301</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122126273</v>
+        <v>122126069</v>
       </c>
       <c r="B10" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1839,25 +1839,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491430</v>
+        <v>491431</v>
       </c>
       <c r="R10" t="n">
-        <v>6278304</v>
+        <v>6278302</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1911,22 +1911,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1971,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126060</v>
+        <v>122125949</v>
       </c>
       <c r="B11" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2028,7 +2028,7 @@
         <v>491410</v>
       </c>
       <c r="R11" t="n">
-        <v>6278308</v>
+        <v>6278312</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122126294</v>
+        <v>122126969</v>
       </c>
       <c r="B12" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R12" t="n">
         <v>6278314</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2259,7 +2259,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122126300</v>
+        <v>122126307</v>
       </c>
       <c r="B13" t="n">
         <v>56290</v>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491409</v>
+        <v>491432</v>
       </c>
       <c r="R13" t="n">
-        <v>6278309</v>
+        <v>6278301</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122126302</v>
+        <v>122126067</v>
       </c>
       <c r="B14" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2415,25 +2415,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491409</v>
+        <v>491431</v>
       </c>
       <c r="R14" t="n">
-        <v>6278308</v>
+        <v>6278305</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2547,10 +2547,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122126307</v>
+        <v>122126976</v>
       </c>
       <c r="B15" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491432</v>
+        <v>491407</v>
       </c>
       <c r="R15" t="n">
-        <v>6278301</v>
+        <v>6278314</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122126066</v>
+        <v>122126981</v>
       </c>
       <c r="B16" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491433</v>
+        <v>491408</v>
       </c>
       <c r="R16" t="n">
-        <v>6278305</v>
+        <v>6278312</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122126072</v>
+        <v>122126300</v>
       </c>
       <c r="B17" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2847,25 +2847,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491432</v>
+        <v>491409</v>
       </c>
       <c r="R17" t="n">
-        <v>6278302</v>
+        <v>6278309</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2979,10 +2979,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122126081</v>
+        <v>122126302</v>
       </c>
       <c r="B18" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2991,25 +2991,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491467</v>
+        <v>491409</v>
       </c>
       <c r="R18" t="n">
-        <v>6278291</v>
+        <v>6278308</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122126082</v>
+        <v>122126297</v>
       </c>
       <c r="B19" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3135,25 +3135,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491466</v>
+        <v>491410</v>
       </c>
       <c r="R19" t="n">
-        <v>6278292</v>
+        <v>6278308</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3267,10 +3267,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122125948</v>
+        <v>122126081</v>
       </c>
       <c r="B20" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3279,25 +3279,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491408</v>
+        <v>491467</v>
       </c>
       <c r="R20" t="n">
-        <v>6278313</v>
+        <v>6278291</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3411,10 +3411,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122126978</v>
+        <v>122126065</v>
       </c>
       <c r="B21" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3423,25 +3423,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491408</v>
+        <v>491433</v>
       </c>
       <c r="R21" t="n">
-        <v>6278313</v>
+        <v>6278303</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122126962</v>
+        <v>122126960</v>
       </c>
       <c r="B22" t="n">
         <v>56278</v>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491408</v>
+        <v>491399</v>
       </c>
       <c r="R22" t="n">
-        <v>6278312</v>
+        <v>6278315</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122126971</v>
+        <v>122126959</v>
       </c>
       <c r="B23" t="n">
         <v>56278</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491408</v>
+        <v>491397</v>
       </c>
       <c r="R23" t="n">
-        <v>6278315</v>
+        <v>6278316</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3843,7 +3843,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122126076</v>
+        <v>122126082</v>
       </c>
       <c r="B24" t="n">
         <v>56271</v>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491469</v>
+        <v>491466</v>
       </c>
       <c r="R24" t="n">
-        <v>6278289</v>
+        <v>6278292</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3987,10 +3987,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122126067</v>
+        <v>122126961</v>
       </c>
       <c r="B25" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3999,25 +3999,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491431</v>
+        <v>491402</v>
       </c>
       <c r="R25" t="n">
-        <v>6278305</v>
+        <v>6278314</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4131,10 +4131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122126065</v>
+        <v>122125950</v>
       </c>
       <c r="B26" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4143,25 +4143,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491433</v>
+        <v>491430</v>
       </c>
       <c r="R26" t="n">
         <v>6278303</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4275,10 +4275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122126961</v>
+        <v>122126144</v>
       </c>
       <c r="B27" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4287,25 +4287,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491402</v>
+        <v>491449</v>
       </c>
       <c r="R27" t="n">
-        <v>6278314</v>
+        <v>6278298</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4359,22 +4359,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122126297</v>
+        <v>122126061</v>
       </c>
       <c r="B28" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4476,7 +4476,7 @@
         <v>491410</v>
       </c>
       <c r="R28" t="n">
-        <v>6278308</v>
+        <v>6278312</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4563,10 +4563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126295</v>
+        <v>122126146</v>
       </c>
       <c r="B29" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4575,25 +4575,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4620,7 +4620,7 @@
         <v>491408</v>
       </c>
       <c r="R29" t="n">
-        <v>6278313</v>
+        <v>6278310</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4647,22 +4647,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4707,10 +4707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122126983</v>
+        <v>122126060</v>
       </c>
       <c r="B30" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4719,25 +4719,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491409</v>
+        <v>491410</v>
       </c>
       <c r="R30" t="n">
         <v>6278308</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4851,10 +4851,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126975</v>
+        <v>122126063</v>
       </c>
       <c r="B31" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4863,25 +4863,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491407</v>
+        <v>491433</v>
       </c>
       <c r="R31" t="n">
-        <v>6278313</v>
+        <v>6278302</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4995,10 +4995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122126960</v>
+        <v>122126290</v>
       </c>
       <c r="B32" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491399</v>
+        <v>491408</v>
       </c>
       <c r="R32" t="n">
-        <v>6278315</v>
+        <v>6278310</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5084,17 +5084,17 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
           <t>23:35</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>23:36</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122126062</v>
+        <v>122126972</v>
       </c>
       <c r="B34" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5295,25 +5295,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491432</v>
+        <v>491408</v>
       </c>
       <c r="R34" t="n">
-        <v>6278301</v>
+        <v>6278314</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122126050</v>
+        <v>122126293</v>
       </c>
       <c r="B35" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5439,25 +5439,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491450</v>
+        <v>491407</v>
       </c>
       <c r="R35" t="n">
-        <v>6278297</v>
+        <v>6278314</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5511,22 +5511,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5571,10 +5571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122126972</v>
+        <v>122126273</v>
       </c>
       <c r="B36" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491408</v>
+        <v>491430</v>
       </c>
       <c r="R36" t="n">
-        <v>6278314</v>
+        <v>6278304</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5655,22 +5655,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5715,10 +5715,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122126305</v>
+        <v>122126971</v>
       </c>
       <c r="B37" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5731,21 +5731,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491431</v>
+        <v>491408</v>
       </c>
       <c r="R37" t="n">
-        <v>6278302</v>
+        <v>6278315</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5859,10 +5859,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122126079</v>
+        <v>122126975</v>
       </c>
       <c r="B38" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5871,25 +5871,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491470</v>
+        <v>491407</v>
       </c>
       <c r="R38" t="n">
-        <v>6278289</v>
+        <v>6278313</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6003,10 +6003,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122126144</v>
+        <v>122126305</v>
       </c>
       <c r="B39" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491449</v>
+        <v>491431</v>
       </c>
       <c r="R39" t="n">
-        <v>6278298</v>
+        <v>6278302</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -6087,22 +6087,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122126982</v>
+        <v>122126271</v>
       </c>
       <c r="B41" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6307,21 +6307,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491409</v>
+        <v>491452</v>
       </c>
       <c r="R41" t="n">
-        <v>6278309</v>
+        <v>6278297</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6375,22 +6375,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6435,10 +6435,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122126146</v>
+        <v>122125947</v>
       </c>
       <c r="B42" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6447,25 +6447,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6492,7 +6492,7 @@
         <v>491408</v>
       </c>
       <c r="R42" t="n">
-        <v>6278310</v>
+        <v>6278313</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6519,22 +6519,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6579,10 +6579,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122126293</v>
+        <v>122126983</v>
       </c>
       <c r="B43" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6595,21 +6595,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491407</v>
+        <v>491409</v>
       </c>
       <c r="R43" t="n">
-        <v>6278314</v>
+        <v>6278308</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6723,10 +6723,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122126271</v>
+        <v>122126147</v>
       </c>
       <c r="B44" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6735,25 +6735,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491452</v>
+        <v>491403</v>
       </c>
       <c r="R44" t="n">
-        <v>6278297</v>
+        <v>6278312</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6807,22 +6807,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6867,10 +6867,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122126272</v>
+        <v>122126079</v>
       </c>
       <c r="B45" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6879,25 +6879,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491444</v>
+        <v>491470</v>
       </c>
       <c r="R45" t="n">
-        <v>6278302</v>
+        <v>6278289</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6951,22 +6951,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7011,10 +7011,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122125950</v>
+        <v>122126066</v>
       </c>
       <c r="B46" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7023,25 +7023,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491430</v>
+        <v>491433</v>
       </c>
       <c r="R46" t="n">
-        <v>6278303</v>
+        <v>6278305</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122126059</v>
+        <v>122126982</v>
       </c>
       <c r="B47" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7167,25 +7167,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491410</v>
+        <v>491409</v>
       </c>
       <c r="R47" t="n">
         <v>6278309</v>
@@ -7244,17 +7244,17 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
           <t>23:31</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>23:32</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122126061</v>
+        <v>122126295</v>
       </c>
       <c r="B48" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7311,25 +7311,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R48" t="n">
-        <v>6278312</v>
+        <v>6278313</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7443,10 +7443,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122125949</v>
+        <v>122126059</v>
       </c>
       <c r="B49" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7455,25 +7455,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7500,7 +7500,7 @@
         <v>491410</v>
       </c>
       <c r="R49" t="n">
-        <v>6278312</v>
+        <v>6278309</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126076</v>
+        <v>122126303</v>
       </c>
       <c r="B2" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491469</v>
+        <v>491410</v>
       </c>
       <c r="R2" t="n">
-        <v>6278289</v>
+        <v>6278309</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,7 +819,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126050</v>
+        <v>122126076</v>
       </c>
       <c r="B3" t="n">
         <v>56271</v>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491450</v>
+        <v>491469</v>
       </c>
       <c r="R3" t="n">
-        <v>6278297</v>
+        <v>6278289</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,22 +903,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,10 +963,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126303</v>
+        <v>122126050</v>
       </c>
       <c r="B4" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,25 +975,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491410</v>
+        <v>491450</v>
       </c>
       <c r="R4" t="n">
-        <v>6278309</v>
+        <v>6278297</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,22 +1047,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -5139,7 +5139,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122126985</v>
+        <v>122126972</v>
       </c>
       <c r="B33" t="n">
         <v>56278</v>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491431</v>
+        <v>491408</v>
       </c>
       <c r="R33" t="n">
-        <v>6278305</v>
+        <v>6278314</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122126972</v>
+        <v>122126293</v>
       </c>
       <c r="B34" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5299,21 +5299,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491408</v>
+        <v>491407</v>
       </c>
       <c r="R34" t="n">
         <v>6278314</v>
@@ -5427,7 +5427,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122126293</v>
+        <v>122126273</v>
       </c>
       <c r="B35" t="n">
         <v>56290</v>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491407</v>
+        <v>491430</v>
       </c>
       <c r="R35" t="n">
-        <v>6278314</v>
+        <v>6278304</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5511,22 +5511,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5571,10 +5571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122126273</v>
+        <v>122126985</v>
       </c>
       <c r="B36" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491430</v>
+        <v>491431</v>
       </c>
       <c r="R36" t="n">
-        <v>6278304</v>
+        <v>6278305</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5655,22 +5655,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -1971,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122125949</v>
+        <v>122126969</v>
       </c>
       <c r="B11" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491410</v>
+        <v>491409</v>
       </c>
       <c r="R11" t="n">
-        <v>6278312</v>
+        <v>6278314</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122126969</v>
+        <v>122126307</v>
       </c>
       <c r="B12" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491409</v>
+        <v>491432</v>
       </c>
       <c r="R12" t="n">
-        <v>6278314</v>
+        <v>6278301</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2259,10 +2259,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122126307</v>
+        <v>122125949</v>
       </c>
       <c r="B13" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491432</v>
+        <v>491410</v>
       </c>
       <c r="R13" t="n">
-        <v>6278301</v>
+        <v>6278312</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122126061</v>
+        <v>122126290</v>
       </c>
       <c r="B28" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R28" t="n">
-        <v>6278312</v>
+        <v>6278310</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4563,7 +4563,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126146</v>
+        <v>122126061</v>
       </c>
       <c r="B29" t="n">
         <v>56271</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491408</v>
+        <v>491410</v>
       </c>
       <c r="R29" t="n">
-        <v>6278310</v>
+        <v>6278312</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4647,22 +4647,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4707,7 +4707,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122126060</v>
+        <v>122126146</v>
       </c>
       <c r="B30" t="n">
         <v>56271</v>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R30" t="n">
-        <v>6278308</v>
+        <v>6278310</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4791,22 +4791,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4851,7 +4851,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126063</v>
+        <v>122126060</v>
       </c>
       <c r="B31" t="n">
         <v>56271</v>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491433</v>
+        <v>491410</v>
       </c>
       <c r="R31" t="n">
-        <v>6278302</v>
+        <v>6278308</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4995,10 +4995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122126290</v>
+        <v>122126063</v>
       </c>
       <c r="B32" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5007,25 +5007,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491408</v>
+        <v>491433</v>
       </c>
       <c r="R32" t="n">
-        <v>6278310</v>
+        <v>6278302</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122126271</v>
+        <v>122125947</v>
       </c>
       <c r="B41" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6307,21 +6307,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491452</v>
+        <v>491408</v>
       </c>
       <c r="R41" t="n">
-        <v>6278297</v>
+        <v>6278313</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6375,22 +6375,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6435,10 +6435,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122125947</v>
+        <v>122126983</v>
       </c>
       <c r="B42" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6451,21 +6451,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R42" t="n">
-        <v>6278313</v>
+        <v>6278308</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6579,10 +6579,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122126983</v>
+        <v>122126271</v>
       </c>
       <c r="B43" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6595,21 +6595,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491409</v>
+        <v>491452</v>
       </c>
       <c r="R43" t="n">
-        <v>6278308</v>
+        <v>6278297</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126303</v>
+        <v>122126982</v>
       </c>
       <c r="B2" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,7 +724,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491410</v>
+        <v>491409</v>
       </c>
       <c r="R2" t="n">
         <v>6278309</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126076</v>
+        <v>122126270</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,25 +826,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -873,10 +863,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491469</v>
+        <v>491452</v>
       </c>
       <c r="R3" t="n">
-        <v>6278289</v>
+        <v>6278297</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,22 +893,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126050</v>
+        <v>122125947</v>
       </c>
       <c r="B4" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,25 +965,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1002,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491450</v>
+        <v>491408</v>
       </c>
       <c r="R4" t="n">
-        <v>6278297</v>
+        <v>6278313</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,22 +1032,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1107,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126272</v>
+        <v>122126965</v>
       </c>
       <c r="B5" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,21 +1108,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1161,10 +1141,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491444</v>
+        <v>491408</v>
       </c>
       <c r="R5" t="n">
-        <v>6278302</v>
+        <v>6278313</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1191,22 +1171,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1269,11 +1249,6 @@
       <c r="E6" t="n">
         <v>205995</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1395,10 +1370,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126965</v>
+        <v>122126297</v>
       </c>
       <c r="B7" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1411,21 +1386,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1449,10 +1419,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491408</v>
+        <v>491410</v>
       </c>
       <c r="R7" t="n">
-        <v>6278313</v>
+        <v>6278308</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1484,7 +1454,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1494,7 +1464,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1539,10 +1509,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126072</v>
+        <v>122126964</v>
       </c>
       <c r="B8" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1551,25 +1521,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1593,10 +1558,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491432</v>
+        <v>491408</v>
       </c>
       <c r="R8" t="n">
-        <v>6278302</v>
+        <v>6278312</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1628,7 +1593,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1638,7 +1603,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1683,10 +1648,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126062</v>
+        <v>122126985</v>
       </c>
       <c r="B9" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1695,25 +1660,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1737,10 +1697,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491432</v>
+        <v>491431</v>
       </c>
       <c r="R9" t="n">
-        <v>6278301</v>
+        <v>6278305</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1772,7 +1732,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1782,7 +1742,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1827,7 +1787,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122126069</v>
+        <v>122126147</v>
       </c>
       <c r="B10" t="n">
         <v>56271</v>
@@ -1845,11 +1805,6 @@
       <c r="E10" t="n">
         <v>205998</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -1881,10 +1836,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491431</v>
+        <v>491403</v>
       </c>
       <c r="R10" t="n">
-        <v>6278302</v>
+        <v>6278312</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1911,22 +1866,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1971,10 +1926,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126969</v>
+        <v>122126301</v>
       </c>
       <c r="B11" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1987,21 +1942,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2028,7 +1978,7 @@
         <v>491409</v>
       </c>
       <c r="R11" t="n">
-        <v>6278314</v>
+        <v>6278308</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2060,7 +2010,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2070,7 +2020,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2133,11 +2083,6 @@
       <c r="E12" t="n">
         <v>205995</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -2259,10 +2204,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122125949</v>
+        <v>122126303</v>
       </c>
       <c r="B13" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2275,21 +2220,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2316,7 +2256,7 @@
         <v>491410</v>
       </c>
       <c r="R13" t="n">
-        <v>6278312</v>
+        <v>6278309</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2403,10 +2343,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122126067</v>
+        <v>122126971</v>
       </c>
       <c r="B14" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2415,25 +2355,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2457,10 +2392,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491431</v>
+        <v>491408</v>
       </c>
       <c r="R14" t="n">
-        <v>6278305</v>
+        <v>6278315</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2492,7 +2427,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2502,7 +2437,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2547,10 +2482,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122126976</v>
+        <v>122126293</v>
       </c>
       <c r="B15" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2563,21 +2498,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2691,10 +2621,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122126981</v>
+        <v>122126064</v>
       </c>
       <c r="B16" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2703,25 +2633,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2745,10 +2670,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491408</v>
+        <v>491433</v>
       </c>
       <c r="R16" t="n">
-        <v>6278312</v>
+        <v>6278303</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2780,7 +2705,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2790,7 +2715,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2835,10 +2760,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122126300</v>
+        <v>122126063</v>
       </c>
       <c r="B17" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2847,25 +2772,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2889,10 +2809,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491409</v>
+        <v>491433</v>
       </c>
       <c r="R17" t="n">
-        <v>6278309</v>
+        <v>6278302</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2924,7 +2844,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2934,7 +2854,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2979,10 +2899,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122126302</v>
+        <v>122126969</v>
       </c>
       <c r="B18" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2995,21 +2915,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3036,7 +2951,7 @@
         <v>491409</v>
       </c>
       <c r="R18" t="n">
-        <v>6278308</v>
+        <v>6278314</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3068,7 +2983,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3078,7 +2993,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3123,10 +3038,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122126297</v>
+        <v>122126972</v>
       </c>
       <c r="B19" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3139,21 +3054,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3177,10 +3087,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R19" t="n">
-        <v>6278308</v>
+        <v>6278314</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3212,7 +3122,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3222,7 +3132,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3267,10 +3177,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122126081</v>
+        <v>122126984</v>
       </c>
       <c r="B20" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3279,25 +3189,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3321,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491467</v>
+        <v>491409</v>
       </c>
       <c r="R20" t="n">
-        <v>6278291</v>
+        <v>6278308</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3356,7 +3261,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3366,7 +3271,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3411,7 +3316,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122126065</v>
+        <v>122126146</v>
       </c>
       <c r="B21" t="n">
         <v>56271</v>
@@ -3429,11 +3334,6 @@
       <c r="E21" t="n">
         <v>205998</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -3465,10 +3365,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491433</v>
+        <v>491408</v>
       </c>
       <c r="R21" t="n">
-        <v>6278303</v>
+        <v>6278310</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3495,22 +3395,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3555,10 +3455,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122126960</v>
+        <v>122126144</v>
       </c>
       <c r="B22" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3567,25 +3467,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3609,10 +3504,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491399</v>
+        <v>491449</v>
       </c>
       <c r="R22" t="n">
-        <v>6278315</v>
+        <v>6278298</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3639,22 +3534,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3699,7 +3594,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122126959</v>
+        <v>122126974</v>
       </c>
       <c r="B23" t="n">
         <v>56278</v>
@@ -3717,11 +3612,6 @@
       <c r="E23" t="n">
         <v>205992</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Myotis daubentonii</t>
@@ -3753,10 +3643,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491397</v>
+        <v>491407</v>
       </c>
       <c r="R23" t="n">
-        <v>6278316</v>
+        <v>6278314</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3788,7 +3678,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3798,7 +3688,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3843,10 +3733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122126082</v>
+        <v>122126295</v>
       </c>
       <c r="B24" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3855,25 +3745,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3897,10 +3782,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491466</v>
+        <v>491408</v>
       </c>
       <c r="R24" t="n">
-        <v>6278292</v>
+        <v>6278313</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3932,7 +3817,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3942,7 +3827,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3987,10 +3872,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122126961</v>
+        <v>122126272</v>
       </c>
       <c r="B25" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4003,21 +3888,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4041,10 +3921,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491402</v>
+        <v>491444</v>
       </c>
       <c r="R25" t="n">
-        <v>6278314</v>
+        <v>6278302</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4071,22 +3951,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4149,11 +4029,6 @@
       <c r="E26" t="n">
         <v>100092</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -4275,10 +4150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122126144</v>
+        <v>122126975</v>
       </c>
       <c r="B27" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4287,25 +4162,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4329,10 +4199,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491449</v>
+        <v>491407</v>
       </c>
       <c r="R27" t="n">
-        <v>6278298</v>
+        <v>6278313</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4359,22 +4229,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4419,7 +4289,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122126290</v>
+        <v>122126292</v>
       </c>
       <c r="B28" t="n">
         <v>56290</v>
@@ -4436,11 +4306,6 @@
       </c>
       <c r="E28" t="n">
         <v>205995</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4563,10 +4428,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126061</v>
+        <v>122126299</v>
       </c>
       <c r="B29" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4575,25 +4440,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4617,10 +4477,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491410</v>
+        <v>491409</v>
       </c>
       <c r="R29" t="n">
-        <v>6278312</v>
+        <v>6278309</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4652,7 +4512,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4662,7 +4522,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4707,7 +4567,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122126146</v>
+        <v>122126081</v>
       </c>
       <c r="B30" t="n">
         <v>56271</v>
@@ -4725,11 +4585,6 @@
       <c r="E30" t="n">
         <v>205998</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -4761,10 +4616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491408</v>
+        <v>491467</v>
       </c>
       <c r="R30" t="n">
-        <v>6278310</v>
+        <v>6278291</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4791,22 +4646,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4851,7 +4706,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126060</v>
+        <v>122126059</v>
       </c>
       <c r="B31" t="n">
         <v>56271</v>
@@ -4869,11 +4724,6 @@
       <c r="E31" t="n">
         <v>205998</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -4908,7 +4758,7 @@
         <v>491410</v>
       </c>
       <c r="R31" t="n">
-        <v>6278308</v>
+        <v>6278309</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4995,7 +4845,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122126063</v>
+        <v>122126068</v>
       </c>
       <c r="B32" t="n">
         <v>56271</v>
@@ -5013,11 +4863,6 @@
       <c r="E32" t="n">
         <v>205998</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -5049,7 +4894,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491433</v>
+        <v>491430</v>
       </c>
       <c r="R32" t="n">
         <v>6278302</v>
@@ -5084,7 +4929,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5094,7 +4939,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5139,10 +4984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122126972</v>
+        <v>122126072</v>
       </c>
       <c r="B33" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5151,25 +4996,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -5193,10 +5033,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491408</v>
+        <v>491432</v>
       </c>
       <c r="R33" t="n">
-        <v>6278314</v>
+        <v>6278302</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5228,7 +5068,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5238,7 +5078,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5283,10 +5123,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122126293</v>
+        <v>122126066</v>
       </c>
       <c r="B34" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5295,25 +5135,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5337,10 +5172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491407</v>
+        <v>491433</v>
       </c>
       <c r="R34" t="n">
-        <v>6278314</v>
+        <v>6278305</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5372,7 +5207,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5382,7 +5217,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5427,10 +5262,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122126273</v>
+        <v>122126959</v>
       </c>
       <c r="B35" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5443,21 +5278,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5481,10 +5311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491430</v>
+        <v>491397</v>
       </c>
       <c r="R35" t="n">
-        <v>6278304</v>
+        <v>6278316</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5511,22 +5341,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5571,7 +5401,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122126985</v>
+        <v>122126960</v>
       </c>
       <c r="B36" t="n">
         <v>56278</v>
@@ -5589,11 +5419,6 @@
       <c r="E36" t="n">
         <v>205992</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Myotis daubentonii</t>
@@ -5625,10 +5450,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491431</v>
+        <v>491399</v>
       </c>
       <c r="R36" t="n">
-        <v>6278305</v>
+        <v>6278315</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5660,7 +5485,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5670,7 +5495,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5715,10 +5540,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122126971</v>
+        <v>122126062</v>
       </c>
       <c r="B37" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5727,25 +5552,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5769,10 +5589,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491408</v>
+        <v>491432</v>
       </c>
       <c r="R37" t="n">
-        <v>6278315</v>
+        <v>6278301</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5804,7 +5624,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5814,7 +5634,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5859,10 +5679,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122126975</v>
+        <v>122126069</v>
       </c>
       <c r="B38" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5871,25 +5691,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5913,10 +5728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491407</v>
+        <v>491431</v>
       </c>
       <c r="R38" t="n">
-        <v>6278313</v>
+        <v>6278302</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5948,7 +5763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5958,7 +5773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6003,10 +5818,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122126305</v>
+        <v>122126961</v>
       </c>
       <c r="B39" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6019,21 +5834,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -6057,10 +5867,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491431</v>
+        <v>491402</v>
       </c>
       <c r="R39" t="n">
-        <v>6278302</v>
+        <v>6278314</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -6092,7 +5902,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6102,7 +5912,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6147,10 +5957,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122126068</v>
+        <v>122126305</v>
       </c>
       <c r="B40" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6159,25 +5969,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6201,7 +6006,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491430</v>
+        <v>491431</v>
       </c>
       <c r="R40" t="n">
         <v>6278302</v>
@@ -6236,7 +6041,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6246,7 +6051,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6291,10 +6096,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122125947</v>
+        <v>122126050</v>
       </c>
       <c r="B41" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6303,25 +6108,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6345,10 +6145,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491408</v>
+        <v>491450</v>
       </c>
       <c r="R41" t="n">
-        <v>6278313</v>
+        <v>6278297</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6375,22 +6175,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6435,10 +6235,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122126983</v>
+        <v>122126061</v>
       </c>
       <c r="B42" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6447,25 +6247,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6489,10 +6284,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491409</v>
+        <v>491410</v>
       </c>
       <c r="R42" t="n">
-        <v>6278308</v>
+        <v>6278312</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6524,17 +6319,17 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
+          <t>23:29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
           <t>23:30</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>23:31</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6579,10 +6374,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122126271</v>
+        <v>122126076</v>
       </c>
       <c r="B43" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6591,25 +6386,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6633,10 +6423,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491452</v>
+        <v>491469</v>
       </c>
       <c r="R43" t="n">
-        <v>6278297</v>
+        <v>6278289</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6663,22 +6453,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6723,7 +6513,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122126147</v>
+        <v>122126082</v>
       </c>
       <c r="B44" t="n">
         <v>56271</v>
@@ -6741,11 +6531,6 @@
       <c r="E44" t="n">
         <v>205998</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -6777,10 +6562,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491403</v>
+        <v>491466</v>
       </c>
       <c r="R44" t="n">
-        <v>6278312</v>
+        <v>6278292</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6807,22 +6592,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6867,10 +6652,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122126079</v>
+        <v>122126273</v>
       </c>
       <c r="B45" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6879,25 +6664,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6921,10 +6701,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491470</v>
+        <v>491430</v>
       </c>
       <c r="R45" t="n">
-        <v>6278289</v>
+        <v>6278304</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6951,22 +6731,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7011,10 +6791,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122126066</v>
+        <v>122125949</v>
       </c>
       <c r="B46" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7023,25 +6803,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7065,10 +6840,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491433</v>
+        <v>491410</v>
       </c>
       <c r="R46" t="n">
-        <v>6278305</v>
+        <v>6278312</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -7100,7 +6875,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7110,7 +6885,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7155,10 +6930,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122126982</v>
+        <v>122126079</v>
       </c>
       <c r="B47" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7167,25 +6942,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7209,10 +6979,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491409</v>
+        <v>491470</v>
       </c>
       <c r="R47" t="n">
-        <v>6278309</v>
+        <v>6278289</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -7244,7 +7014,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7254,7 +7024,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7299,10 +7069,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122126295</v>
+        <v>122126060</v>
       </c>
       <c r="B48" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7311,25 +7081,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7353,10 +7118,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491408</v>
+        <v>491410</v>
       </c>
       <c r="R48" t="n">
-        <v>6278313</v>
+        <v>6278308</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -7388,17 +7153,17 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
           <t>23:32</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>23:33</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7443,7 +7208,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122126059</v>
+        <v>122126067</v>
       </c>
       <c r="B49" t="n">
         <v>56271</v>
@@ -7461,11 +7226,6 @@
       <c r="E49" t="n">
         <v>205998</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -7497,10 +7257,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491410</v>
+        <v>491431</v>
       </c>
       <c r="R49" t="n">
-        <v>6278309</v>
+        <v>6278305</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7532,7 +7292,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7542,7 +7302,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126982</v>
+        <v>122126270</v>
       </c>
       <c r="B2" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491409</v>
+        <v>491452</v>
       </c>
       <c r="R2" t="n">
-        <v>6278309</v>
+        <v>6278297</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -814,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126270</v>
+        <v>122126982</v>
       </c>
       <c r="B3" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491452</v>
+        <v>491409</v>
       </c>
       <c r="R3" t="n">
-        <v>6278297</v>
+        <v>6278309</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,22 +893,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4150,10 +4150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122126975</v>
+        <v>122126081</v>
       </c>
       <c r="B27" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4162,20 +4162,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491407</v>
+        <v>491467</v>
       </c>
       <c r="R27" t="n">
-        <v>6278313</v>
+        <v>6278291</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4289,10 +4289,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122126292</v>
+        <v>122126059</v>
       </c>
       <c r="B28" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4301,20 +4301,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491408</v>
+        <v>491410</v>
       </c>
       <c r="R28" t="n">
-        <v>6278310</v>
+        <v>6278309</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4428,10 +4428,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126299</v>
+        <v>122126068</v>
       </c>
       <c r="B29" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4440,20 +4440,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491409</v>
+        <v>491430</v>
       </c>
       <c r="R29" t="n">
-        <v>6278309</v>
+        <v>6278302</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4567,10 +4567,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122126081</v>
+        <v>122126975</v>
       </c>
       <c r="B30" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4579,20 +4579,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491467</v>
+        <v>491407</v>
       </c>
       <c r="R30" t="n">
-        <v>6278291</v>
+        <v>6278313</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4706,10 +4706,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126059</v>
+        <v>122126292</v>
       </c>
       <c r="B31" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4718,20 +4718,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R31" t="n">
-        <v>6278309</v>
+        <v>6278310</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4845,10 +4845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122126068</v>
+        <v>122126299</v>
       </c>
       <c r="B32" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4857,20 +4857,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491430</v>
+        <v>491409</v>
       </c>
       <c r="R32" t="n">
-        <v>6278302</v>
+        <v>6278309</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -6513,10 +6513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122126082</v>
+        <v>122126273</v>
       </c>
       <c r="B44" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6562,10 +6562,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491466</v>
+        <v>491430</v>
       </c>
       <c r="R44" t="n">
-        <v>6278292</v>
+        <v>6278304</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6592,22 +6592,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6652,10 +6652,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122126273</v>
+        <v>122126082</v>
       </c>
       <c r="B45" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6664,20 +6664,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491430</v>
+        <v>491466</v>
       </c>
       <c r="R45" t="n">
-        <v>6278304</v>
+        <v>6278292</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6731,22 +6731,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -1231,7 +1231,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126294</v>
+        <v>122126297</v>
       </c>
       <c r="B6" t="n">
         <v>56290</v>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491408</v>
+        <v>491410</v>
       </c>
       <c r="R6" t="n">
-        <v>6278314</v>
+        <v>6278308</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1315,17 +1315,17 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>23:32</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>23:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1370,7 +1370,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126297</v>
+        <v>122126294</v>
       </c>
       <c r="B7" t="n">
         <v>56290</v>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R7" t="n">
-        <v>6278308</v>
+        <v>6278314</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3594,10 +3594,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122126974</v>
+        <v>122126295</v>
       </c>
       <c r="B23" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3610,16 +3610,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491407</v>
+        <v>491408</v>
       </c>
       <c r="R23" t="n">
-        <v>6278314</v>
+        <v>6278313</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122126295</v>
+        <v>122126974</v>
       </c>
       <c r="B24" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3749,16 +3749,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491408</v>
+        <v>491407</v>
       </c>
       <c r="R24" t="n">
-        <v>6278313</v>
+        <v>6278314</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122126081</v>
+        <v>122126975</v>
       </c>
       <c r="B27" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4162,20 +4162,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491467</v>
+        <v>491407</v>
       </c>
       <c r="R27" t="n">
-        <v>6278291</v>
+        <v>6278313</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4289,10 +4289,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122126059</v>
+        <v>122126292</v>
       </c>
       <c r="B28" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4301,20 +4301,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R28" t="n">
-        <v>6278309</v>
+        <v>6278310</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4428,10 +4428,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126068</v>
+        <v>122126299</v>
       </c>
       <c r="B29" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4440,20 +4440,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491430</v>
+        <v>491409</v>
       </c>
       <c r="R29" t="n">
-        <v>6278302</v>
+        <v>6278309</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4567,10 +4567,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122126975</v>
+        <v>122126081</v>
       </c>
       <c r="B30" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4579,20 +4579,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491407</v>
+        <v>491467</v>
       </c>
       <c r="R30" t="n">
-        <v>6278313</v>
+        <v>6278291</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4706,10 +4706,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126292</v>
+        <v>122126059</v>
       </c>
       <c r="B31" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4718,20 +4718,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491408</v>
+        <v>491410</v>
       </c>
       <c r="R31" t="n">
-        <v>6278310</v>
+        <v>6278309</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4845,10 +4845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122126299</v>
+        <v>122126068</v>
       </c>
       <c r="B32" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4857,20 +4857,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491409</v>
+        <v>491430</v>
       </c>
       <c r="R32" t="n">
-        <v>6278309</v>
+        <v>6278302</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126270</v>
+        <v>122126978</v>
       </c>
       <c r="B2" t="n">
-        <v>56290</v>
+        <v>56282</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>205992</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491452</v>
+        <v>491408</v>
       </c>
       <c r="R2" t="n">
-        <v>6278297</v>
+        <v>6278313</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -814,10 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126982</v>
+        <v>122125950</v>
       </c>
       <c r="B3" t="n">
-        <v>56278</v>
+        <v>56289</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,16 +835,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>100092</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -863,10 +873,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491409</v>
+        <v>491430</v>
       </c>
       <c r="R3" t="n">
-        <v>6278309</v>
+        <v>6278303</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -908,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -953,10 +963,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122125947</v>
+        <v>122126272</v>
       </c>
       <c r="B4" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,16 +979,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1002,10 +1017,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491408</v>
+        <v>491444</v>
       </c>
       <c r="R4" t="n">
-        <v>6278313</v>
+        <v>6278302</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1032,22 +1047,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1092,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126965</v>
+        <v>122125948</v>
       </c>
       <c r="B5" t="n">
-        <v>56278</v>
+        <v>56289</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,16 +1123,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205992</v>
+        <v>100092</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1231,10 +1251,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126297</v>
+        <v>122126976</v>
       </c>
       <c r="B6" t="n">
-        <v>56290</v>
+        <v>56282</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1247,16 +1267,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>205992</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1280,10 +1305,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491410</v>
+        <v>491407</v>
       </c>
       <c r="R6" t="n">
-        <v>6278308</v>
+        <v>6278314</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1315,7 +1340,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1325,7 +1350,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1370,10 +1395,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126294</v>
+        <v>122126063</v>
       </c>
       <c r="B7" t="n">
-        <v>56290</v>
+        <v>56275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,20 +1407,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>205998</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1419,10 +1449,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491408</v>
+        <v>491433</v>
       </c>
       <c r="R7" t="n">
-        <v>6278314</v>
+        <v>6278302</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1454,7 +1484,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1464,7 +1494,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1509,10 +1539,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126964</v>
+        <v>122126066</v>
       </c>
       <c r="B8" t="n">
-        <v>56278</v>
+        <v>56275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1521,20 +1551,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205992</v>
+        <v>205998</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1558,10 +1593,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491408</v>
+        <v>491433</v>
       </c>
       <c r="R8" t="n">
-        <v>6278312</v>
+        <v>6278305</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1593,7 +1628,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1603,7 +1638,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1648,10 +1683,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126985</v>
+        <v>122126980</v>
       </c>
       <c r="B9" t="n">
-        <v>56278</v>
+        <v>56282</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1666,6 +1701,11 @@
       <c r="E9" t="n">
         <v>205992</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Myotis daubentonii</t>
@@ -1697,10 +1737,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491431</v>
+        <v>491408</v>
       </c>
       <c r="R9" t="n">
-        <v>6278305</v>
+        <v>6278312</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1732,7 +1772,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1742,7 +1782,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1787,10 +1827,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122126147</v>
+        <v>122126297</v>
       </c>
       <c r="B10" t="n">
-        <v>56271</v>
+        <v>56294</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1799,20 +1839,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>205995</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1836,10 +1881,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491403</v>
+        <v>491410</v>
       </c>
       <c r="R10" t="n">
-        <v>6278312</v>
+        <v>6278308</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1866,22 +1911,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1926,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126301</v>
+        <v>122126298</v>
       </c>
       <c r="B11" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1944,6 +1989,11 @@
       <c r="E11" t="n">
         <v>205995</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1975,10 +2025,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491409</v>
+        <v>491410</v>
       </c>
       <c r="R11" t="n">
-        <v>6278308</v>
+        <v>6278309</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2010,7 +2060,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2020,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2065,10 +2115,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122126307</v>
+        <v>122126270</v>
       </c>
       <c r="B12" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2083,6 +2133,11 @@
       <c r="E12" t="n">
         <v>205995</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -2114,10 +2169,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491432</v>
+        <v>491452</v>
       </c>
       <c r="R12" t="n">
-        <v>6278301</v>
+        <v>6278297</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2144,22 +2199,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2204,10 +2259,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122126303</v>
+        <v>122126070</v>
       </c>
       <c r="B13" t="n">
-        <v>56290</v>
+        <v>56275</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2216,20 +2271,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205995</v>
+        <v>205998</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2253,10 +2313,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491410</v>
+        <v>491431</v>
       </c>
       <c r="R13" t="n">
-        <v>6278309</v>
+        <v>6278302</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2288,7 +2348,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2298,7 +2358,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2343,10 +2403,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122126971</v>
+        <v>122126972</v>
       </c>
       <c r="B14" t="n">
-        <v>56278</v>
+        <v>56282</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2361,6 +2421,11 @@
       <c r="E14" t="n">
         <v>205992</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Myotis daubentonii</t>
@@ -2395,7 +2460,7 @@
         <v>491408</v>
       </c>
       <c r="R14" t="n">
-        <v>6278315</v>
+        <v>6278314</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2482,10 +2547,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122126293</v>
+        <v>122126295</v>
       </c>
       <c r="B15" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2500,6 +2565,11 @@
       <c r="E15" t="n">
         <v>205995</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -2531,10 +2601,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491407</v>
+        <v>491408</v>
       </c>
       <c r="R15" t="n">
-        <v>6278314</v>
+        <v>6278313</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2621,10 +2691,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122126064</v>
+        <v>122126079</v>
       </c>
       <c r="B16" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2639,6 +2709,11 @@
       <c r="E16" t="n">
         <v>205998</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -2670,10 +2745,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491433</v>
+        <v>491470</v>
       </c>
       <c r="R16" t="n">
-        <v>6278303</v>
+        <v>6278289</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2705,7 +2780,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2715,7 +2790,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2760,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122126063</v>
+        <v>122126072</v>
       </c>
       <c r="B17" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2778,6 +2853,11 @@
       <c r="E17" t="n">
         <v>205998</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -2809,7 +2889,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491433</v>
+        <v>491432</v>
       </c>
       <c r="R17" t="n">
         <v>6278302</v>
@@ -2844,7 +2924,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2854,7 +2934,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2899,10 +2979,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122126969</v>
+        <v>122126294</v>
       </c>
       <c r="B18" t="n">
-        <v>56278</v>
+        <v>56294</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2915,16 +2995,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>205995</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2948,7 +3033,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491409</v>
+        <v>491408</v>
       </c>
       <c r="R18" t="n">
         <v>6278314</v>
@@ -2983,17 +3068,17 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
+          <t>23:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>23:33</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>23:34</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3038,10 +3123,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122126972</v>
+        <v>122126060</v>
       </c>
       <c r="B19" t="n">
-        <v>56278</v>
+        <v>56275</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3050,20 +3135,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205992</v>
+        <v>205998</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3087,10 +3177,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491408</v>
+        <v>491410</v>
       </c>
       <c r="R19" t="n">
-        <v>6278314</v>
+        <v>6278308</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3122,17 +3212,17 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>23:32</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>23:33</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3177,10 +3267,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122126984</v>
+        <v>122126302</v>
       </c>
       <c r="B20" t="n">
-        <v>56278</v>
+        <v>56294</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3193,16 +3283,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205992</v>
+        <v>205995</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3316,10 +3411,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122126146</v>
+        <v>122126971</v>
       </c>
       <c r="B21" t="n">
-        <v>56271</v>
+        <v>56282</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3328,20 +3423,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205998</v>
+        <v>205992</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3368,7 +3468,7 @@
         <v>491408</v>
       </c>
       <c r="R21" t="n">
-        <v>6278310</v>
+        <v>6278315</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3395,22 +3495,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3455,10 +3555,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122126144</v>
+        <v>122126984</v>
       </c>
       <c r="B22" t="n">
-        <v>56271</v>
+        <v>56282</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3467,20 +3567,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205998</v>
+        <v>205992</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3504,10 +3609,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491449</v>
+        <v>491409</v>
       </c>
       <c r="R22" t="n">
-        <v>6278298</v>
+        <v>6278308</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3534,22 +3639,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3594,10 +3699,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122126295</v>
+        <v>122126959</v>
       </c>
       <c r="B23" t="n">
-        <v>56290</v>
+        <v>56282</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3610,16 +3715,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205995</v>
+        <v>205992</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3643,10 +3753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491408</v>
+        <v>491397</v>
       </c>
       <c r="R23" t="n">
-        <v>6278313</v>
+        <v>6278316</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3678,7 +3788,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3688,7 +3798,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3733,10 +3843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122126974</v>
+        <v>122126969</v>
       </c>
       <c r="B24" t="n">
-        <v>56278</v>
+        <v>56282</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3751,6 +3861,11 @@
       <c r="E24" t="n">
         <v>205992</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Myotis daubentonii</t>
@@ -3782,7 +3897,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491407</v>
+        <v>491409</v>
       </c>
       <c r="R24" t="n">
         <v>6278314</v>
@@ -3817,7 +3932,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3827,7 +3942,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3872,10 +3987,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122126272</v>
+        <v>122126300</v>
       </c>
       <c r="B25" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3890,6 +4005,11 @@
       <c r="E25" t="n">
         <v>205995</v>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -3921,10 +4041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491444</v>
+        <v>491409</v>
       </c>
       <c r="R25" t="n">
-        <v>6278302</v>
+        <v>6278309</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3951,22 +4071,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4011,10 +4131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122125950</v>
+        <v>122126308</v>
       </c>
       <c r="B26" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4027,16 +4147,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4060,10 +4185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491430</v>
+        <v>491432</v>
       </c>
       <c r="R26" t="n">
-        <v>6278303</v>
+        <v>6278301</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4095,7 +4220,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4105,7 +4230,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4150,10 +4275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122126975</v>
+        <v>122126050</v>
       </c>
       <c r="B27" t="n">
-        <v>56278</v>
+        <v>56275</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4162,20 +4287,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205992</v>
+        <v>205998</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4199,10 +4329,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491407</v>
+        <v>491450</v>
       </c>
       <c r="R27" t="n">
-        <v>6278313</v>
+        <v>6278297</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4229,22 +4359,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4289,10 +4419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122126292</v>
+        <v>122126982</v>
       </c>
       <c r="B28" t="n">
-        <v>56290</v>
+        <v>56282</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4305,16 +4435,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>205995</v>
+        <v>205992</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4338,10 +4473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R28" t="n">
-        <v>6278310</v>
+        <v>6278309</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4373,7 +4508,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4383,7 +4518,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4428,10 +4563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126299</v>
+        <v>122126960</v>
       </c>
       <c r="B29" t="n">
-        <v>56290</v>
+        <v>56282</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4444,16 +4579,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205995</v>
+        <v>205992</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4477,10 +4617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491409</v>
+        <v>491399</v>
       </c>
       <c r="R29" t="n">
-        <v>6278309</v>
+        <v>6278315</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4512,7 +4652,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4522,7 +4662,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4567,10 +4707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122126081</v>
+        <v>122126061</v>
       </c>
       <c r="B30" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4585,6 +4725,11 @@
       <c r="E30" t="n">
         <v>205998</v>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -4616,10 +4761,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491467</v>
+        <v>491410</v>
       </c>
       <c r="R30" t="n">
-        <v>6278291</v>
+        <v>6278312</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4651,7 +4796,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4661,7 +4806,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4706,10 +4851,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126059</v>
+        <v>122126146</v>
       </c>
       <c r="B31" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4724,6 +4869,11 @@
       <c r="E31" t="n">
         <v>205998</v>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -4755,10 +4905,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R31" t="n">
-        <v>6278309</v>
+        <v>6278310</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4785,22 +4935,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4845,10 +4995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122126068</v>
+        <v>122126059</v>
       </c>
       <c r="B32" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4863,6 +5013,11 @@
       <c r="E32" t="n">
         <v>205998</v>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -4894,10 +5049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491430</v>
+        <v>491410</v>
       </c>
       <c r="R32" t="n">
-        <v>6278302</v>
+        <v>6278309</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4929,7 +5084,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4939,7 +5094,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4984,10 +5139,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122126072</v>
+        <v>122126065</v>
       </c>
       <c r="B33" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5002,6 +5157,11 @@
       <c r="E33" t="n">
         <v>205998</v>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -5033,10 +5193,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491432</v>
+        <v>491433</v>
       </c>
       <c r="R33" t="n">
-        <v>6278302</v>
+        <v>6278303</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5068,7 +5228,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5078,7 +5238,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5123,10 +5283,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122126066</v>
+        <v>122126291</v>
       </c>
       <c r="B34" t="n">
-        <v>56271</v>
+        <v>56294</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5135,20 +5295,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205998</v>
+        <v>205995</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5172,10 +5337,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491433</v>
+        <v>491408</v>
       </c>
       <c r="R34" t="n">
-        <v>6278305</v>
+        <v>6278310</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5207,7 +5372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5217,7 +5382,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5262,10 +5427,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122126959</v>
+        <v>122126293</v>
       </c>
       <c r="B35" t="n">
-        <v>56278</v>
+        <v>56294</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5278,16 +5443,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>205992</v>
+        <v>205995</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5311,10 +5481,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491397</v>
+        <v>491407</v>
       </c>
       <c r="R35" t="n">
-        <v>6278316</v>
+        <v>6278314</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5346,7 +5516,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5356,7 +5526,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5401,10 +5571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122126960</v>
+        <v>122126062</v>
       </c>
       <c r="B36" t="n">
-        <v>56278</v>
+        <v>56275</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5413,20 +5583,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>205992</v>
+        <v>205998</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5450,10 +5625,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491399</v>
+        <v>491432</v>
       </c>
       <c r="R36" t="n">
-        <v>6278315</v>
+        <v>6278301</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5485,7 +5660,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5495,7 +5670,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5540,10 +5715,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122126062</v>
+        <v>122126961</v>
       </c>
       <c r="B37" t="n">
-        <v>56271</v>
+        <v>56282</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5552,20 +5727,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>205998</v>
+        <v>205992</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5589,10 +5769,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491432</v>
+        <v>491402</v>
       </c>
       <c r="R37" t="n">
-        <v>6278301</v>
+        <v>6278314</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5624,7 +5804,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5634,7 +5814,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5679,10 +5859,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122126069</v>
+        <v>122126082</v>
       </c>
       <c r="B38" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5697,6 +5877,11 @@
       <c r="E38" t="n">
         <v>205998</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -5728,10 +5913,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491431</v>
+        <v>491466</v>
       </c>
       <c r="R38" t="n">
-        <v>6278302</v>
+        <v>6278292</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5763,7 +5948,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5773,7 +5958,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5818,10 +6003,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122126961</v>
+        <v>122126305</v>
       </c>
       <c r="B39" t="n">
-        <v>56278</v>
+        <v>56294</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5834,16 +6019,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>205992</v>
+        <v>205995</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5867,10 +6057,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491402</v>
+        <v>491431</v>
       </c>
       <c r="R39" t="n">
-        <v>6278314</v>
+        <v>6278302</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5902,7 +6092,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5912,7 +6102,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5957,10 +6147,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122126305</v>
+        <v>122126076</v>
       </c>
       <c r="B40" t="n">
-        <v>56290</v>
+        <v>56275</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5969,20 +6159,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>205995</v>
+        <v>205998</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6006,10 +6201,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491431</v>
+        <v>491469</v>
       </c>
       <c r="R40" t="n">
-        <v>6278302</v>
+        <v>6278289</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -6041,7 +6236,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6051,7 +6246,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6096,10 +6291,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122126050</v>
+        <v>122126147</v>
       </c>
       <c r="B41" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6114,6 +6309,11 @@
       <c r="E41" t="n">
         <v>205998</v>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -6145,10 +6345,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491450</v>
+        <v>491403</v>
       </c>
       <c r="R41" t="n">
-        <v>6278297</v>
+        <v>6278312</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6175,22 +6375,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6235,10 +6435,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122126061</v>
+        <v>122125949</v>
       </c>
       <c r="B42" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6247,20 +6447,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6374,10 +6579,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122126076</v>
+        <v>122126068</v>
       </c>
       <c r="B43" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6392,6 +6597,11 @@
       <c r="E43" t="n">
         <v>205998</v>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -6423,10 +6633,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491469</v>
+        <v>491430</v>
       </c>
       <c r="R43" t="n">
-        <v>6278289</v>
+        <v>6278302</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6458,7 +6668,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6468,7 +6678,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6516,7 +6726,7 @@
         <v>122126273</v>
       </c>
       <c r="B44" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6530,6 +6740,11 @@
       </c>
       <c r="E44" t="n">
         <v>205995</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -6652,10 +6867,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122126082</v>
+        <v>122126067</v>
       </c>
       <c r="B45" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6670,6 +6885,11 @@
       <c r="E45" t="n">
         <v>205998</v>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -6701,10 +6921,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491466</v>
+        <v>491431</v>
       </c>
       <c r="R45" t="n">
-        <v>6278292</v>
+        <v>6278305</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6736,7 +6956,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6746,7 +6966,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6791,10 +7011,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122125949</v>
+        <v>122126144</v>
       </c>
       <c r="B46" t="n">
-        <v>56285</v>
+        <v>56275</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6803,20 +7023,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100092</v>
+        <v>205998</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6840,10 +7065,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491410</v>
+        <v>491449</v>
       </c>
       <c r="R46" t="n">
-        <v>6278312</v>
+        <v>6278298</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6870,22 +7095,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6930,10 +7155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122126079</v>
+        <v>122126081</v>
       </c>
       <c r="B47" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6948,6 +7173,11 @@
       <c r="E47" t="n">
         <v>205998</v>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -6979,10 +7209,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491470</v>
+        <v>491467</v>
       </c>
       <c r="R47" t="n">
-        <v>6278289</v>
+        <v>6278291</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -7014,17 +7244,17 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
           <t>23:21</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>23:22</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7069,10 +7299,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122126060</v>
+        <v>122126985</v>
       </c>
       <c r="B48" t="n">
-        <v>56271</v>
+        <v>56282</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7081,20 +7311,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205998</v>
+        <v>205992</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7118,10 +7353,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491410</v>
+        <v>491431</v>
       </c>
       <c r="R48" t="n">
-        <v>6278308</v>
+        <v>6278305</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -7153,7 +7388,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7163,7 +7398,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7208,10 +7443,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122126067</v>
+        <v>122126975</v>
       </c>
       <c r="B49" t="n">
-        <v>56271</v>
+        <v>56282</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7220,20 +7455,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>205998</v>
+        <v>205992</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7257,10 +7497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491431</v>
+        <v>491407</v>
       </c>
       <c r="R49" t="n">
-        <v>6278305</v>
+        <v>6278313</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7292,7 +7532,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7302,7 +7542,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 27463-2023 artfynd.xlsx
+++ b/artfynd/A 27463-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126978</v>
+        <v>122126291</v>
       </c>
       <c r="B2" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -732,7 +732,7 @@
         <v>491408</v>
       </c>
       <c r="R2" t="n">
-        <v>6278313</v>
+        <v>6278310</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,10 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122125950</v>
+        <v>122126299</v>
       </c>
       <c r="B3" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,21 +835,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491430</v>
+        <v>491409</v>
       </c>
       <c r="R3" t="n">
-        <v>6278303</v>
+        <v>6278309</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,10 +963,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126272</v>
+        <v>122125950</v>
       </c>
       <c r="B4" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491444</v>
+        <v>491430</v>
       </c>
       <c r="R4" t="n">
-        <v>6278302</v>
+        <v>6278303</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,22 +1047,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122125948</v>
+        <v>122126969</v>
       </c>
       <c r="B5" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491408</v>
+        <v>491409</v>
       </c>
       <c r="R5" t="n">
-        <v>6278313</v>
+        <v>6278314</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1251,7 +1251,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126976</v>
+        <v>122126981</v>
       </c>
       <c r="B6" t="n">
         <v>56282</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491407</v>
+        <v>491408</v>
       </c>
       <c r="R6" t="n">
-        <v>6278314</v>
+        <v>6278312</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1340,17 +1340,17 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>23:32</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>23:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1395,7 +1395,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126063</v>
+        <v>122126064</v>
       </c>
       <c r="B7" t="n">
         <v>56275</v>
@@ -1452,7 +1452,7 @@
         <v>491433</v>
       </c>
       <c r="R7" t="n">
-        <v>6278302</v>
+        <v>6278303</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126066</v>
+        <v>122126068</v>
       </c>
       <c r="B8" t="n">
         <v>56275</v>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491433</v>
+        <v>491430</v>
       </c>
       <c r="R8" t="n">
-        <v>6278305</v>
+        <v>6278302</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1628,17 +1628,17 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>23:25</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>23:26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126980</v>
+        <v>122126144</v>
       </c>
       <c r="B9" t="n">
-        <v>56282</v>
+        <v>56275</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491408</v>
+        <v>491449</v>
       </c>
       <c r="R9" t="n">
-        <v>6278312</v>
+        <v>6278298</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122126297</v>
+        <v>122125949</v>
       </c>
       <c r="B10" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1884,7 +1884,7 @@
         <v>491410</v>
       </c>
       <c r="R10" t="n">
-        <v>6278308</v>
+        <v>6278312</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1971,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126298</v>
+        <v>122126971</v>
       </c>
       <c r="B11" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491410</v>
+        <v>491408</v>
       </c>
       <c r="R11" t="n">
-        <v>6278309</v>
+        <v>6278315</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122126270</v>
+        <v>122126081</v>
       </c>
       <c r="B12" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491452</v>
+        <v>491467</v>
       </c>
       <c r="R12" t="n">
-        <v>6278297</v>
+        <v>6278291</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2199,22 +2199,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2259,7 +2259,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122126070</v>
+        <v>122126067</v>
       </c>
       <c r="B13" t="n">
         <v>56275</v>
@@ -2316,7 +2316,7 @@
         <v>491431</v>
       </c>
       <c r="R13" t="n">
-        <v>6278302</v>
+        <v>6278305</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122126972</v>
+        <v>122126072</v>
       </c>
       <c r="B14" t="n">
-        <v>56282</v>
+        <v>56275</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2415,25 +2415,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491408</v>
+        <v>491432</v>
       </c>
       <c r="R14" t="n">
-        <v>6278314</v>
+        <v>6278302</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2547,10 +2547,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122126295</v>
+        <v>122126079</v>
       </c>
       <c r="B15" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2559,25 +2559,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491408</v>
+        <v>491470</v>
       </c>
       <c r="R15" t="n">
-        <v>6278313</v>
+        <v>6278289</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122126079</v>
+        <v>122125948</v>
       </c>
       <c r="B16" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491470</v>
+        <v>491408</v>
       </c>
       <c r="R16" t="n">
-        <v>6278289</v>
+        <v>6278313</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122126072</v>
+        <v>122126305</v>
       </c>
       <c r="B17" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2847,25 +2847,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491432</v>
+        <v>491431</v>
       </c>
       <c r="R17" t="n">
         <v>6278302</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2979,7 +2979,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122126294</v>
+        <v>122126303</v>
       </c>
       <c r="B18" t="n">
         <v>56294</v>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491408</v>
+        <v>491410</v>
       </c>
       <c r="R18" t="n">
-        <v>6278314</v>
+        <v>6278309</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3123,7 +3123,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122126060</v>
+        <v>122126082</v>
       </c>
       <c r="B19" t="n">
         <v>56275</v>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491410</v>
+        <v>491466</v>
       </c>
       <c r="R19" t="n">
-        <v>6278308</v>
+        <v>6278292</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3267,10 +3267,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122126302</v>
+        <v>122126050</v>
       </c>
       <c r="B20" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3279,25 +3279,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491409</v>
+        <v>491450</v>
       </c>
       <c r="R20" t="n">
-        <v>6278308</v>
+        <v>6278297</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3351,22 +3351,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3411,10 +3411,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122126971</v>
+        <v>122126293</v>
       </c>
       <c r="B21" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491408</v>
+        <v>491407</v>
       </c>
       <c r="R21" t="n">
-        <v>6278315</v>
+        <v>6278314</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122126984</v>
+        <v>122126982</v>
       </c>
       <c r="B22" t="n">
         <v>56282</v>
@@ -3612,7 +3612,7 @@
         <v>491409</v>
       </c>
       <c r="R22" t="n">
-        <v>6278308</v>
+        <v>6278309</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122126959</v>
+        <v>122126978</v>
       </c>
       <c r="B23" t="n">
         <v>56282</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491397</v>
+        <v>491408</v>
       </c>
       <c r="R23" t="n">
-        <v>6278316</v>
+        <v>6278313</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3843,7 +3843,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122126969</v>
+        <v>122126985</v>
       </c>
       <c r="B24" t="n">
         <v>56282</v>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491409</v>
+        <v>491431</v>
       </c>
       <c r="R24" t="n">
-        <v>6278314</v>
+        <v>6278305</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3987,10 +3987,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122126300</v>
+        <v>122126063</v>
       </c>
       <c r="B25" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3999,25 +3999,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491409</v>
+        <v>491433</v>
       </c>
       <c r="R25" t="n">
-        <v>6278309</v>
+        <v>6278302</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4275,10 +4275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122126050</v>
+        <v>122126295</v>
       </c>
       <c r="B27" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4287,25 +4287,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491450</v>
+        <v>491408</v>
       </c>
       <c r="R27" t="n">
-        <v>6278297</v>
+        <v>6278313</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4359,22 +4359,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122126982</v>
+        <v>122126297</v>
       </c>
       <c r="B28" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4435,21 +4435,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491409</v>
+        <v>491410</v>
       </c>
       <c r="R28" t="n">
-        <v>6278309</v>
+        <v>6278308</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4563,7 +4563,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122126960</v>
+        <v>122126974</v>
       </c>
       <c r="B29" t="n">
         <v>56282</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491399</v>
+        <v>491407</v>
       </c>
       <c r="R29" t="n">
-        <v>6278315</v>
+        <v>6278314</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4707,7 +4707,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122126061</v>
+        <v>122126147</v>
       </c>
       <c r="B30" t="n">
         <v>56275</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491410</v>
+        <v>491403</v>
       </c>
       <c r="R30" t="n">
         <v>6278312</v>
@@ -4791,22 +4791,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4851,10 +4851,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122126146</v>
+        <v>122126294</v>
       </c>
       <c r="B31" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4863,25 +4863,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4908,7 +4908,7 @@
         <v>491408</v>
       </c>
       <c r="R31" t="n">
-        <v>6278310</v>
+        <v>6278314</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4935,22 +4935,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4995,7 +4995,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122126059</v>
+        <v>122126061</v>
       </c>
       <c r="B32" t="n">
         <v>56275</v>
@@ -5052,7 +5052,7 @@
         <v>491410</v>
       </c>
       <c r="R32" t="n">
-        <v>6278309</v>
+        <v>6278312</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>23:32</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5139,7 +5139,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122126065</v>
+        <v>122126060</v>
       </c>
       <c r="B33" t="n">
         <v>56275</v>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491433</v>
+        <v>491410</v>
       </c>
       <c r="R33" t="n">
-        <v>6278303</v>
+        <v>6278308</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122126291</v>
+        <v>122126960</v>
       </c>
       <c r="B34" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5299,21 +5299,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491408</v>
+        <v>491399</v>
       </c>
       <c r="R34" t="n">
-        <v>6278310</v>
+        <v>6278315</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122126293</v>
+        <v>122126975</v>
       </c>
       <c r="B35" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5484,7 +5484,7 @@
         <v>491407</v>
       </c>
       <c r="R35" t="n">
-        <v>6278314</v>
+        <v>6278313</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5571,7 +5571,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122126062</v>
+        <v>122126070</v>
       </c>
       <c r="B36" t="n">
         <v>56275</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491432</v>
+        <v>491431</v>
       </c>
       <c r="R36" t="n">
-        <v>6278301</v>
+        <v>6278302</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5715,10 +5715,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122126961</v>
+        <v>122126273</v>
       </c>
       <c r="B37" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5731,21 +5731,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491402</v>
+        <v>491430</v>
       </c>
       <c r="R37" t="n">
-        <v>6278314</v>
+        <v>6278304</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5799,22 +5799,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5859,10 +5859,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122126082</v>
+        <v>122126972</v>
       </c>
       <c r="B38" t="n">
-        <v>56275</v>
+        <v>56282</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5871,25 +5871,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491466</v>
+        <v>491408</v>
       </c>
       <c r="R38" t="n">
-        <v>6278292</v>
+        <v>6278314</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6003,7 +6003,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122126305</v>
+        <v>122126270</v>
       </c>
       <c r="B39" t="n">
         <v>56294</v>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491431</v>
+        <v>491452</v>
       </c>
       <c r="R39" t="n">
-        <v>6278302</v>
+        <v>6278297</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -6087,22 +6087,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6147,10 +6147,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122126076</v>
+        <v>122126272</v>
       </c>
       <c r="B40" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6159,25 +6159,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491469</v>
+        <v>491444</v>
       </c>
       <c r="R40" t="n">
-        <v>6278289</v>
+        <v>6278302</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -6231,22 +6231,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122126147</v>
+        <v>122126301</v>
       </c>
       <c r="B41" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6303,25 +6303,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491403</v>
+        <v>491409</v>
       </c>
       <c r="R41" t="n">
-        <v>6278312</v>
+        <v>6278308</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6375,22 +6375,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6435,10 +6435,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122125949</v>
+        <v>122126984</v>
       </c>
       <c r="B42" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6451,21 +6451,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491410</v>
+        <v>491409</v>
       </c>
       <c r="R42" t="n">
-        <v>6278312</v>
+        <v>6278308</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6579,7 +6579,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122126068</v>
+        <v>122126076</v>
       </c>
       <c r="B43" t="n">
         <v>56275</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491430</v>
+        <v>491469</v>
       </c>
       <c r="R43" t="n">
-        <v>6278302</v>
+        <v>6278289</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6723,10 +6723,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122126273</v>
+        <v>122126062</v>
       </c>
       <c r="B44" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6735,25 +6735,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491430</v>
+        <v>491432</v>
       </c>
       <c r="R44" t="n">
-        <v>6278304</v>
+        <v>6278301</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6807,22 +6807,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6867,7 +6867,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122126067</v>
+        <v>122126146</v>
       </c>
       <c r="B45" t="n">
         <v>56275</v>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491431</v>
+        <v>491408</v>
       </c>
       <c r="R45" t="n">
-        <v>6278305</v>
+        <v>6278310</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6951,22 +6951,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7011,10 +7011,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122126144</v>
+        <v>122126959</v>
       </c>
       <c r="B46" t="n">
-        <v>56275</v>
+        <v>56282</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7023,25 +7023,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491449</v>
+        <v>491397</v>
       </c>
       <c r="R46" t="n">
-        <v>6278298</v>
+        <v>6278316</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -7095,22 +7095,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122126081</v>
+        <v>122126961</v>
       </c>
       <c r="B47" t="n">
-        <v>56275</v>
+        <v>56282</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7167,25 +7167,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491467</v>
+        <v>491402</v>
       </c>
       <c r="R47" t="n">
-        <v>6278291</v>
+        <v>6278314</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>23:21</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122126985</v>
+        <v>122126066</v>
       </c>
       <c r="B48" t="n">
-        <v>56282</v>
+        <v>56275</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7311,25 +7311,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491431</v>
+        <v>491433</v>
       </c>
       <c r="R48" t="n">
         <v>6278305</v>
@@ -7443,10 +7443,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122126975</v>
+        <v>122126059</v>
       </c>
       <c r="B49" t="n">
-        <v>56282</v>
+        <v>56275</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7455,25 +7455,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491407</v>
+        <v>491410</v>
       </c>
       <c r="R49" t="n">
-        <v>6278313</v>
+        <v>6278309</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7532,17 +7532,17 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
           <t>23:32</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>23:33</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
